--- a/apps/deep/www/calculators/interior-plateau.xlsx
+++ b/apps/deep/www/calculators/interior-plateau.xlsx
@@ -16,25 +16,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="curve_key">'Reference'!$A$5:$A$33</definedName>
-    <definedName name="curve_x1">'Reference'!$G$5:$G$33</definedName>
-    <definedName name="curve_y1">'Reference'!$O$5:$O$33</definedName>
-    <definedName name="curve_x2">'Reference'!$H$5:$H$33</definedName>
-    <definedName name="curve_y2">'Reference'!$P$5:$P$33</definedName>
-    <definedName name="curve_x3">'Reference'!$I$5:$I$33</definedName>
-    <definedName name="curve_y3">'Reference'!$Q$5:$Q$33</definedName>
-    <definedName name="curve_x4">'Reference'!$J$5:$J$33</definedName>
-    <definedName name="curve_y4">'Reference'!$R$5:$R$33</definedName>
-    <definedName name="curve_x5">'Reference'!$K$5:$K$33</definedName>
-    <definedName name="curve_y5">'Reference'!$S$5:$S$33</definedName>
-    <definedName name="curve_x6">'Reference'!$L$5:$L$33</definedName>
-    <definedName name="curve_y6">'Reference'!$T$5:$T$33</definedName>
-    <definedName name="curve_x7">'Reference'!$M$5:$M$33</definedName>
-    <definedName name="curve_y7">'Reference'!$U$5:$U$33</definedName>
-    <definedName name="curve_x8">'Reference'!$N$5:$N$33</definedName>
-    <definedName name="curve_y8">'Reference'!$V$5:$V$33</definedName>
-    <definedName name="idx_spring_pctag2019ws">'Metrics'!$V$5</definedName>
-    <definedName name="idx_spring_pctimp2019ws">'Metrics'!$V$6</definedName>
+    <definedName name="curve_key">'Reference'!$A$5:$A$34</definedName>
+    <definedName name="curve_x1">'Reference'!$G$5:$G$34</definedName>
+    <definedName name="curve_y1">'Reference'!$O$5:$O$34</definedName>
+    <definedName name="curve_x2">'Reference'!$H$5:$H$34</definedName>
+    <definedName name="curve_y2">'Reference'!$P$5:$P$34</definedName>
+    <definedName name="curve_x3">'Reference'!$I$5:$I$34</definedName>
+    <definedName name="curve_y3">'Reference'!$Q$5:$Q$34</definedName>
+    <definedName name="curve_x4">'Reference'!$J$5:$J$34</definedName>
+    <definedName name="curve_y4">'Reference'!$R$5:$R$34</definedName>
+    <definedName name="curve_x5">'Reference'!$K$5:$K$34</definedName>
+    <definedName name="curve_y5">'Reference'!$S$5:$S$34</definedName>
+    <definedName name="curve_x6">'Reference'!$L$5:$L$34</definedName>
+    <definedName name="curve_y6">'Reference'!$T$5:$T$34</definedName>
+    <definedName name="curve_x7">'Reference'!$M$5:$M$34</definedName>
+    <definedName name="curve_y7">'Reference'!$U$5:$U$34</definedName>
+    <definedName name="curve_x8">'Reference'!$N$5:$N$34</definedName>
+    <definedName name="curve_y8">'Reference'!$V$5:$V$34</definedName>
+    <definedName name="idx_spring_pctimp2019ws">'Metrics'!$V$5</definedName>
+    <definedName name="idx_spring_pctag2019ws">'Metrics'!$V$6</definedName>
     <definedName name="idx_spring_pctwet2019ws">'Metrics'!$V$7</definedName>
     <definedName name="idx_spring_rddensws">'Metrics'!$V$8</definedName>
     <definedName name="idx_spring_bfiws">'Metrics'!$V$9</definedName>
@@ -52,16 +52,17 @@
     <definedName name="idx_spring_chem_chla">'Metrics'!$V$21</definedName>
     <definedName name="idx_spring_phab_xcdenmid">'Metrics'!$V$22</definedName>
     <definedName name="idx_spring_phab_xcmgw">'Metrics'!$V$23</definedName>
-    <definedName name="idx_spring_chem_ptl">'Metrics'!$V$24</definedName>
-    <definedName name="idx_spring_chem_cond">'Metrics'!$V$25</definedName>
-    <definedName name="idx_spring_chem_ph">'Metrics'!$V$26</definedName>
-    <definedName name="idx_spring_chem_turb">'Metrics'!$V$27</definedName>
-    <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$28</definedName>
-    <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$29</definedName>
-    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$30</definedName>
-    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$31</definedName>
-    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$32</definedName>
-    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$33</definedName>
+    <definedName name="idx_spring_chem_ntl">'Metrics'!$V$24</definedName>
+    <definedName name="idx_spring_chem_ptl">'Metrics'!$V$25</definedName>
+    <definedName name="idx_spring_chem_cond">'Metrics'!$V$26</definedName>
+    <definedName name="idx_spring_chem_ph">'Metrics'!$V$27</definedName>
+    <definedName name="idx_spring_chem_turb">'Metrics'!$V$28</definedName>
+    <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$29</definedName>
+    <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$30</definedName>
+    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$31</definedName>
+    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$32</definedName>
+    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$33</definedName>
+    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$34</definedName>
     <definedName name="fs_catchment_hydrology">'Results'!$B$4</definedName>
     <definedName name="fs_surface_water_storage">'Results'!$B$5</definedName>
     <definedName name="fs_reach_inflow">'Results'!$B$6</definedName>
@@ -91,14 +92,14 @@
     <definedName name="site_coords">'DEEP Score'!$B$7</definedName>
     <definedName name="site_date">'DEEP Score'!$B$8</definedName>
     <definedName name="site_assessor">'DEEP Score'!$B$9</definedName>
-    <definedName name="in_spring_pctag2019ws">'DEEP Score'!$E$12</definedName>
-    <definedName name="in_spring_pctimp2019ws">'DEEP Score'!$E$13</definedName>
+    <definedName name="in_spring_pctimp2019ws">'DEEP Score'!$E$12</definedName>
+    <definedName name="in_spring_pctag2019ws">'DEEP Score'!$E$13</definedName>
     <definedName name="in_spring_pctwet2019ws">'DEEP Score'!$E$14</definedName>
     <definedName name="in_spring_rddensws">'DEEP Score'!$E$15</definedName>
     <definedName name="in_spring_bfiws">'DEEP Score'!$E$16</definedName>
     <definedName name="in_spring_dorws">'DEEP Score'!$E$17</definedName>
-    <definedName name="in_spring_phab_bfwd_rat">'DEEP Score'!$E$18</definedName>
-    <definedName name="in_spring_phab_rp100_cm">'DEEP Score'!$E$19</definedName>
+    <definedName name="in_spring_phab_bfwd_rat">'DEEP Score'!$E$19</definedName>
+    <definedName name="in_spring_phab_rp100_cm">'DEEP Score'!$E$20</definedName>
     <definedName name="in_spring_phab_xbkf_h">'DEEP Score'!$E$23</definedName>
     <definedName name="in_spring_phab_pct_safn">'DEEP Score'!$E$24</definedName>
     <definedName name="in_spring_phab_xembed">'DEEP Score'!$E$25</definedName>
@@ -110,16 +111,17 @@
     <definedName name="in_spring_chem_chla">'DEEP Score'!$E$35</definedName>
     <definedName name="in_spring_phab_xcdenmid">'DEEP Score'!$E$36</definedName>
     <definedName name="in_spring_phab_xcmgw">'DEEP Score'!$E$37</definedName>
-    <definedName name="in_spring_chem_ptl">'DEEP Score'!$E$38</definedName>
-    <definedName name="in_spring_chem_cond">'DEEP Score'!$E$39</definedName>
-    <definedName name="in_spring_chem_ph">'DEEP Score'!$E$40</definedName>
-    <definedName name="in_spring_chem_turb">'DEEP Score'!$E$41</definedName>
-    <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$42</definedName>
-    <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$43</definedName>
-    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$44</definedName>
-    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$45</definedName>
-    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$46</definedName>
-    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$47</definedName>
+    <definedName name="in_spring_chem_ntl">'DEEP Score'!$E$38</definedName>
+    <definedName name="in_spring_chem_ptl">'DEEP Score'!$E$39</definedName>
+    <definedName name="in_spring_chem_cond">'DEEP Score'!$E$40</definedName>
+    <definedName name="in_spring_chem_ph">'DEEP Score'!$E$41</definedName>
+    <definedName name="in_spring_chem_turb">'DEEP Score'!$E$42</definedName>
+    <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$43</definedName>
+    <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$44</definedName>
+    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$45</definedName>
+    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$46</definedName>
+    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$47</definedName>
+    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$48</definedName>
     <definedName name="site_notes">'DEEP Score'!$A$64</definedName>
     <definedName name="meta_assessment_id">'Metadata'!$B$4</definedName>
     <definedName name="meta_assessment_name">'Metadata'!$B$5</definedName>
@@ -624,6 +626,12 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -641,12 +649,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -656,14 +658,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1529,10 +1531,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Reference condition. Reference curves are built from least-disturbed stations chosen by a fixed landscape-pressure screen. Where this ecoregion has too few, comparable stations of its Level II and then its Level I ecoregion are used, and a metric with no defensible pool is not scored. Landscape pressure metrics are scored on fixed criteria.</t>
+          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 25 borrow comparable least-disturbed stations from a parent ecoregion, stating the level and the transfer risk. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1644,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Version 4 | StreamCurves reference-curve development</t>
+          <t>Version 5 | USEPA NRSA 2013-24 (L3 ecoregion 71), StreamCurves regional analysis, methodology 0.13-provisional</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1758,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Agriculture, crop and hay</t>
+          <t>Impervious surface</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -1784,7 +1786,7 @@
       <c r="B13" s="20" t="n"/>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>Impervious surface</t>
+          <t>Agriculture, crop and hay</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -1944,14 +1946,21 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Bankfull width:depth ratio</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="15" t="inlineStr"/>
+          <t>Base flow index</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" s="37">
+        <f>IF('DEEP Score'!$E$16="","",'DEEP Score'!$E$16)</f>
+        <v/>
+      </c>
+      <c r="F18" s="38" t="inlineStr"/>
       <c r="G18" s="16">
-        <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
+        <f>IF('Metrics'!$V$9="","",'Metrics'!$V$9)</f>
         <v/>
       </c>
       <c r="H18" s="17">
@@ -1964,47 +1973,40 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="37" t="n"/>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>Residual pool depth</t>
-        </is>
-      </c>
-      <c r="D19" s="40" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="42" t="inlineStr"/>
-      <c r="G19" s="43">
-        <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
-        <v/>
-      </c>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="44" t="n"/>
+      <c r="A19" s="39" t="n"/>
+      <c r="B19" s="40" t="n"/>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Bankfull width:depth ratio</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr"/>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="44" t="inlineStr"/>
+      <c r="G19" s="45">
+        <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
+        <v/>
+      </c>
+      <c r="H19" s="40" t="n"/>
+      <c r="I19" s="46" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="n"/>
       <c r="B20" s="20" t="n"/>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Base flow index</t>
+          <t>Residual pool depth</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E20" s="45">
-        <f>IF('DEEP Score'!$E$16="","",'DEEP Score'!$E$16)</f>
-        <v/>
-      </c>
-      <c r="F20" s="46" t="inlineStr"/>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="24" t="inlineStr"/>
       <c r="G20" s="25">
-        <f>IF('Metrics'!$V$9="","",'Metrics'!$V$9)</f>
+        <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
         <v/>
       </c>
       <c r="H20" s="20" t="n"/>
@@ -2032,12 +2034,12 @@
         </is>
       </c>
       <c r="E21" s="48">
-        <f>IF('DEEP Score'!$E$13="","",'DEEP Score'!$E$13)</f>
+        <f>IF('DEEP Score'!$E$12="","",'DEEP Score'!$E$12)</f>
         <v/>
       </c>
       <c r="F21" s="49" t="inlineStr"/>
       <c r="G21" s="33">
-        <f>IF('Metrics'!$V$6="","",'Metrics'!$V$6)</f>
+        <f>IF('Metrics'!$V$5="","",'Metrics'!$V$5)</f>
         <v/>
       </c>
       <c r="H21" s="34">
@@ -2066,11 +2068,11 @@
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="50">
-        <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
-        <v/>
-      </c>
-      <c r="F22" s="51" t="inlineStr"/>
+      <c r="E22" s="37">
+        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
+        <v/>
+      </c>
+      <c r="F22" s="38" t="inlineStr"/>
       <c r="G22" s="16">
         <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
         <v/>
@@ -2165,7 +2167,7 @@
       <c r="I25" s="26" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="inlineStr">
+      <c r="A26" s="50" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
@@ -2181,11 +2183,11 @@
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="50">
-        <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
-        <v/>
-      </c>
-      <c r="F26" s="51" t="inlineStr"/>
+      <c r="E26" s="37">
+        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
+        <v/>
+      </c>
+      <c r="F26" s="38" t="inlineStr"/>
       <c r="G26" s="16">
         <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
         <v/>
@@ -2212,11 +2214,11 @@
           <t>m</t>
         </is>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="51">
         <f>IF('DEEP Score'!$E$23="","",'DEEP Score'!$E$23)</f>
         <v/>
       </c>
-      <c r="F27" s="46" t="inlineStr"/>
+      <c r="F27" s="52" t="inlineStr"/>
       <c r="G27" s="25">
         <f>IF('Metrics'!$V$13="","",'Metrics'!$V$13)</f>
         <v/>
@@ -2225,7 +2227,7 @@
       <c r="I27" s="26" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="inlineStr">
+      <c r="A28" s="50" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
@@ -2279,7 +2281,7 @@
       <c r="I29" s="26" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="inlineStr">
+      <c r="A30" s="50" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
@@ -2327,11 +2329,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E31" s="45">
+      <c r="E31" s="51">
         <f>IF('DEEP Score'!$E$24="","",'DEEP Score'!$E$24)</f>
         <v/>
       </c>
-      <c r="F31" s="46" t="inlineStr"/>
+      <c r="F31" s="52" t="inlineStr"/>
       <c r="G31" s="25">
         <f>IF('Metrics'!$V$14="","",'Metrics'!$V$14)</f>
         <v/>
@@ -2340,7 +2342,7 @@
       <c r="I31" s="26" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="inlineStr">
+      <c r="A32" s="50" t="inlineStr">
         <is>
           <t>Geomorphology</t>
         </is>
@@ -2376,26 +2378,26 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="n"/>
-      <c r="B33" s="38" t="n"/>
-      <c r="C33" s="39" t="inlineStr">
+      <c r="A33" s="39" t="n"/>
+      <c r="B33" s="40" t="n"/>
+      <c r="C33" s="41" t="inlineStr">
         <is>
           <t>Large wood volume</t>
         </is>
       </c>
-      <c r="D33" s="40" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>m3/100m</t>
         </is>
       </c>
-      <c r="E33" s="41" t="n"/>
-      <c r="F33" s="42" t="inlineStr"/>
-      <c r="G33" s="43">
+      <c r="E33" s="43" t="n"/>
+      <c r="F33" s="44" t="inlineStr"/>
+      <c r="G33" s="45">
         <f>IF('Metrics'!$V$20="","",'Metrics'!$V$20)</f>
         <v/>
       </c>
-      <c r="H33" s="38" t="n"/>
-      <c r="I33" s="44" t="n"/>
+      <c r="H33" s="40" t="n"/>
+      <c r="I33" s="46" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="19" t="n"/>
@@ -2410,11 +2412,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E34" s="45">
+      <c r="E34" s="51">
         <f>IF('DEEP Score'!$E$25="","",'DEEP Score'!$E$25)</f>
         <v/>
       </c>
-      <c r="F34" s="46" t="inlineStr"/>
+      <c r="F34" s="52" t="inlineStr"/>
       <c r="G34" s="25">
         <f>IF('Metrics'!$V$15="","",'Metrics'!$V$15)</f>
         <v/>
@@ -2517,351 +2519,358 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="54" t="inlineStr">
+      <c r="A38" s="53" t="inlineStr">
         <is>
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Nutrient cycling</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Total nitrogen</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>mg N/L</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="15" t="inlineStr"/>
+      <c r="G38" s="16">
+        <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
+        <v/>
+      </c>
+      <c r="I38" s="18">
+        <f>IF('DEEP Score'!$H$38="","",IF('DEEP Score'!$H$38&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$38&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>Total phosphorus</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>ug/L</t>
         </is>
       </c>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="32" t="inlineStr"/>
-      <c r="G38" s="33">
-        <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
-        <v/>
-      </c>
-      <c r="H38" s="34">
-        <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
-        <v/>
-      </c>
-      <c r="I38" s="35">
-        <f>IF('DEEP Score'!$H$38="","",IF('DEEP Score'!$H$38&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$38&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="53" t="inlineStr">
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="24" t="inlineStr"/>
+      <c r="G39" s="25">
+        <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
+        <v/>
+      </c>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="53" t="inlineStr">
         <is>
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Water &amp; soil quality</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Specific conductivity</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>uS/cm</t>
         </is>
       </c>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="15" t="inlineStr"/>
-      <c r="G39" s="16">
-        <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
-        <v/>
-      </c>
-      <c r="H39" s="17">
+      <c r="E40" s="14" t="n"/>
+      <c r="F40" s="15" t="inlineStr"/>
+      <c r="G40" s="16">
+        <f>IF('Metrics'!$V$26="","",'Metrics'!$V$26)</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
         <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
         <v/>
       </c>
-      <c r="I39" s="18">
-        <f>IF('DEEP Score'!$H$39="","",IF('DEEP Score'!$H$39&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$39&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="37" t="n"/>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="39" t="inlineStr">
+      <c r="I40" s="18">
+        <f>IF('DEEP Score'!$H$40="","",IF('DEEP Score'!$H$40&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$40&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="n"/>
+      <c r="B41" s="40" t="n"/>
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="D40" s="40" t="inlineStr">
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>Std. Units</t>
         </is>
       </c>
-      <c r="E40" s="41" t="n"/>
-      <c r="F40" s="42" t="inlineStr"/>
-      <c r="G40" s="43">
-        <f>IF('Metrics'!$V$26="","",'Metrics'!$V$26)</f>
-        <v/>
-      </c>
-      <c r="H40" s="38" t="n"/>
-      <c r="I40" s="44" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="n"/>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="E41" s="43" t="n"/>
+      <c r="F41" s="44" t="inlineStr"/>
+      <c r="G41" s="45">
+        <f>IF('Metrics'!$V$27="","",'Metrics'!$V$27)</f>
+        <v/>
+      </c>
+      <c r="H41" s="40" t="n"/>
+      <c r="I41" s="46" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>Turbidity</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>NTU</t>
         </is>
       </c>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="24" t="inlineStr"/>
-      <c r="G41" s="25">
-        <f>IF('Metrics'!$V$27="","",'Metrics'!$V$27)</f>
-        <v/>
-      </c>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="26" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="24" t="inlineStr"/>
+      <c r="G42" s="25">
+        <f>IF('Metrics'!$V$28="","",'Metrics'!$V$28)</f>
+        <v/>
+      </c>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="55" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>Habitat provision</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Fast-water / riffle habitat</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="15" t="inlineStr"/>
-      <c r="G42" s="16">
-        <f>IF('Metrics'!$V$28="","",'Metrics'!$V$28)</f>
-        <v/>
-      </c>
-      <c r="H42" s="17">
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="15" t="inlineStr"/>
+      <c r="G43" s="16">
+        <f>IF('Metrics'!$V$29="","",'Metrics'!$V$29)</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
         <f>IF('Results'!$B$20="","",'Results'!$B$20)</f>
         <v/>
       </c>
-      <c r="I42" s="18">
-        <f>IF('DEEP Score'!$H$42="","",IF('DEEP Score'!$H$42&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$42&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="19" t="n"/>
-      <c r="B43" s="20" t="n"/>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="I43" s="18">
+        <f>IF('DEEP Score'!$H$43="","",IF('DEEP Score'!$H$43&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$43&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>Natural fish cover</t>
         </is>
       </c>
-      <c r="D43" s="22" t="inlineStr">
+      <c r="D44" s="22" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="E43" s="23" t="n"/>
-      <c r="F43" s="24" t="inlineStr"/>
-      <c r="G43" s="25">
-        <f>IF('Metrics'!$V$29="","",'Metrics'!$V$29)</f>
-        <v/>
-      </c>
-      <c r="H43" s="20" t="n"/>
-      <c r="I43" s="26" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="56" t="inlineStr">
+      <c r="E44" s="23" t="n"/>
+      <c r="F44" s="24" t="inlineStr"/>
+      <c r="G44" s="25">
+        <f>IF('Metrics'!$V$30="","",'Metrics'!$V$30)</f>
+        <v/>
+      </c>
+      <c r="H44" s="20" t="n"/>
+      <c r="I44" s="26" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="56" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>Population support</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
         <is>
           <t>Native fish taxa richness</t>
         </is>
       </c>
-      <c r="D44" s="30" t="inlineStr"/>
-      <c r="E44" s="31" t="n"/>
-      <c r="F44" s="32" t="inlineStr"/>
-      <c r="G44" s="33">
-        <f>IF('Metrics'!$V$30="","",'Metrics'!$V$30)</f>
-        <v/>
-      </c>
-      <c r="H44" s="34">
+      <c r="D45" s="30" t="inlineStr"/>
+      <c r="E45" s="31" t="n"/>
+      <c r="F45" s="32" t="inlineStr"/>
+      <c r="G45" s="33">
+        <f>IF('Metrics'!$V$31="","",'Metrics'!$V$31)</f>
+        <v/>
+      </c>
+      <c r="H45" s="34">
         <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
         <v/>
       </c>
-      <c r="I44" s="35">
-        <f>IF('DEEP Score'!$H$44="","",IF('DEEP Score'!$H$44&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$44&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="55" t="inlineStr">
+      <c r="I45" s="35">
+        <f>IF('DEEP Score'!$H$45="","",IF('DEEP Score'!$H$45&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$45&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="55" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>Community dynamics</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>EPT taxa richness</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="15" t="inlineStr"/>
-      <c r="G45" s="16">
-        <f>IF('Metrics'!$V$31="","",'Metrics'!$V$31)</f>
-        <v/>
-      </c>
-      <c r="H45" s="17">
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="15" t="inlineStr"/>
+      <c r="G46" s="16">
+        <f>IF('Metrics'!$V$32="","",'Metrics'!$V$32)</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
         <f>IF('Results'!$B$22="","",'Results'!$B$22)</f>
         <v/>
       </c>
-      <c r="I45" s="18">
-        <f>IF('DEEP Score'!$H$45="","",IF('DEEP Score'!$H$45&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$45&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="n"/>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="I46" s="18">
+        <f>IF('DEEP Score'!$H$46="","",IF('DEEP Score'!$H$46&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$46&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="21" t="inlineStr">
         <is>
           <t>Shannon diversity (H')</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>H'</t>
         </is>
       </c>
-      <c r="E46" s="23" t="n"/>
-      <c r="F46" s="24" t="inlineStr"/>
-      <c r="G46" s="25">
-        <f>IF('Metrics'!$V$32="","",'Metrics'!$V$32)</f>
-        <v/>
-      </c>
-      <c r="H46" s="20" t="n"/>
-      <c r="I46" s="26" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="56" t="inlineStr">
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="24" t="inlineStr"/>
+      <c r="G47" s="25">
+        <f>IF('Metrics'!$V$33="","",'Metrics'!$V$33)</f>
+        <v/>
+      </c>
+      <c r="H47" s="20" t="n"/>
+      <c r="I47" s="26" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B47" s="28" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>Watershed connectivity</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="D47" s="30" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>dams</t>
         </is>
       </c>
-      <c r="E47" s="31" t="n"/>
-      <c r="F47" s="32" t="inlineStr"/>
-      <c r="G47" s="33">
-        <f>IF('Metrics'!$V$33="","",'Metrics'!$V$33)</f>
-        <v/>
-      </c>
-      <c r="H47" s="34">
+      <c r="E48" s="31" t="n"/>
+      <c r="F48" s="32" t="inlineStr"/>
+      <c r="G48" s="33">
+        <f>IF('Metrics'!$V$34="","",'Metrics'!$V$34)</f>
+        <v/>
+      </c>
+      <c r="H48" s="34">
         <f>IF('Results'!$B$23="","",'Results'!$B$23)</f>
         <v/>
       </c>
-      <c r="I47" s="35">
-        <f>IF('DEEP Score'!$H$47="","",IF('DEEP Score'!$H$47&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$47&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="57" t="inlineStr">
+      <c r="I48" s="35">
+        <f>IF('DEEP Score'!$H$48="","",IF('DEEP Score'!$H$48&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$48&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="57" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Sub-index (0 to 1)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="58" t="inlineStr">
-        <is>
-          <t>Physical</t>
-        </is>
-      </c>
-      <c r="B51" s="59">
-        <f>'Results'!$B$26</f>
-        <v/>
-      </c>
-      <c r="C51" s="40">
-        <f>IF('DEEP Score'!$B$51&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$51&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
-        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="58" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="B52" s="59">
-        <f>'Results'!$B$27</f>
-        <v/>
-      </c>
-      <c r="C52" s="40">
+        <f>'Results'!$B$26</f>
+        <v/>
+      </c>
+      <c r="C52" s="42">
         <f>IF('DEEP Score'!$B$52&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$52&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
@@ -2869,91 +2878,94 @@
     <row r="53">
       <c r="A53" s="58" t="inlineStr">
         <is>
+          <t>Chemical</t>
+        </is>
+      </c>
+      <c r="B53" s="59">
+        <f>'Results'!$B$27</f>
+        <v/>
+      </c>
+      <c r="C53" s="42">
+        <f>IF('DEEP Score'!$B$53&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$53&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="58" t="inlineStr">
+        <is>
           <t>Biological</t>
         </is>
       </c>
-      <c r="B53" s="59">
+      <c r="B54" s="59">
         <f>'Results'!$B$28</f>
         <v/>
       </c>
-      <c r="C53" s="40">
-        <f>IF('DEEP Score'!$B$53&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$53&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="60" t="inlineStr">
+      <c r="C54" s="42">
+        <f>IF('DEEP Score'!$B$54&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$54&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="60" t="inlineStr">
         <is>
           <t>Ecosystem Condition Index</t>
         </is>
       </c>
-      <c r="B54" s="61">
+      <c r="B55" s="61">
         <f>'Results'!$B$29</f>
         <v/>
       </c>
-      <c r="C54" s="40">
-        <f>IF('DEEP Score'!$B$54&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$54&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Functions with a score: </t>
-        </is>
-      </c>
-      <c r="B55" s="4">
-        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
+      <c r="C55" s="42">
+        <f>IF('DEEP Score'!$B$55&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$55&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Functions with a score: </t>
+        </is>
+      </c>
+      <c r="B56" s="4">
+        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>This assessment covers 20 of 20 STAF functions.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="62" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="62" t="inlineStr">
         <is>
           <t>Withheld for insufficient reference support (not scored)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Tolerant individuals (%) ~ HBI</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Community dynamics</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Benthic total taxa richness</t>
+          <t>Tolerant individuals (%) ~ HBI</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Population support</t>
+          <t>Community dynamics</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dissolved nitrogen</t>
+          <t>Benthic total taxa richness</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Nutrient cycling</t>
+          <t>Population support</t>
         </is>
       </c>
     </row>
@@ -3032,46 +3044,50 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
-  <mergeCells count="58">
+  <mergeCells count="62">
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I45:I46"/>
     <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="H43:H44"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="B40:B42"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A45:A46"/>
     <mergeCell ref="I16:I17"/>
+    <mergeCell ref="B46:B47"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="H32:H34"/>
     <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B38:B39"/>
     <mergeCell ref="I26:I27"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="I28:I29"/>
     <mergeCell ref="H35:H36"/>
+    <mergeCell ref="I40:I42"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="I12:I13"/>
+    <mergeCell ref="H46:H47"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="A46:A47"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="I24:I25"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="I43:I44"/>
     <mergeCell ref="A64:I69"/>
-    <mergeCell ref="A39:A41"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="H16:H17"/>
-    <mergeCell ref="A42:A43"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="I38:I39"/>
     <mergeCell ref="H28:H29"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="H24:H25"/>
@@ -3080,19 +3096,19 @@
     <mergeCell ref="I32:I34"/>
     <mergeCell ref="I35:I36"/>
     <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H40:H42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A38:A39"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H39:H41"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="H42:H43"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B26:B27"/>
+    <mergeCell ref="I46:I47"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
-  <conditionalFormatting sqref="G12:G47">
+  <conditionalFormatting sqref="G12:G48">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(G12),G12&lt;=0.39)</formula>
     </cfRule>
@@ -3103,7 +3119,7 @@
       <formula>AND(ISNUMBER(G12),G12&gt;0.69)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H47">
+  <conditionalFormatting sqref="H12:H48">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(ISNUMBER(H12),H12&lt;=5)</formula>
     </cfRule>
@@ -3114,7 +3130,7 @@
       <formula>AND(ISNUMBER(H12),H12&gt;10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I47">
+  <conditionalFormatting sqref="I12:I48">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>I12="Non-Functioning"</formula>
     </cfRule>
@@ -3136,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3271,9 +3287,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
-        <is>
-          <t>Agriculture, crop and hay</t>
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>Impervious surface</t>
         </is>
       </c>
       <c r="B5" s="73">
@@ -3285,11 +3301,11 @@
         <v/>
       </c>
       <c r="D5" s="73">
-        <f>"spring_pctag2019ws|"&amp;'Metrics'!$C$5</f>
+        <f>"spring_pctimp2019ws|"&amp;'Metrics'!$C$5</f>
         <v/>
       </c>
       <c r="E5" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$5,curve_key,0),MATCH("spring_pctag2019ws|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$5,curve_key,0),MATCH("spring_pctimp2019ws|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F5" s="73">
@@ -3362,9 +3378,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>Impervious surface</t>
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Agriculture, crop and hay</t>
         </is>
       </c>
       <c r="B6" s="73">
@@ -3376,11 +3392,11 @@
         <v/>
       </c>
       <c r="D6" s="73">
-        <f>"spring_pctimp2019ws|"&amp;'Metrics'!$C$6</f>
+        <f>"spring_pctag2019ws|"&amp;'Metrics'!$C$6</f>
         <v/>
       </c>
       <c r="E6" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$6,curve_key,0),MATCH("spring_pctimp2019ws|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$6,curve_key,0),MATCH("spring_pctag2019ws|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F6" s="73">
@@ -3453,7 +3469,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Wetland</t>
         </is>
@@ -3544,7 +3560,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Road density</t>
         </is>
@@ -3635,7 +3651,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Base flow index</t>
         </is>
@@ -3726,7 +3742,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Degree of regulation</t>
         </is>
@@ -3817,13 +3833,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
       <c r="B11" s="73">
-        <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
+        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
         <v/>
       </c>
       <c r="C11" s="73">
@@ -3908,13 +3924,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Residual pool depth</t>
         </is>
       </c>
       <c r="B12" s="73">
-        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
+        <f>IF('DEEP Score'!$E$20="","",'DEEP Score'!$E$20)</f>
         <v/>
       </c>
       <c r="C12" s="73">
@@ -3999,7 +4015,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Bankfull height above channel</t>
         </is>
@@ -4090,7 +4106,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Sand + fines</t>
         </is>
@@ -4181,7 +4197,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Embeddedness</t>
         </is>
@@ -4272,7 +4288,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Sinuosity</t>
         </is>
@@ -4363,7 +4379,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Bank angle</t>
         </is>
@@ -4454,7 +4470,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Relative bed stability</t>
         </is>
@@ -4545,7 +4561,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Substrate size</t>
         </is>
@@ -4636,7 +4652,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Large wood volume</t>
         </is>
@@ -4727,7 +4743,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Chlorophyll a</t>
         </is>
@@ -4818,7 +4834,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Canopy density, mid-channel</t>
         </is>
@@ -4909,7 +4925,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Riparian veg cover, woody</t>
         </is>
@@ -5000,9 +5016,9 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t>Total phosphorus</t>
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>Total nitrogen</t>
         </is>
       </c>
       <c r="B24" s="73">
@@ -5014,11 +5030,11 @@
         <v/>
       </c>
       <c r="D24" s="73">
-        <f>"spring_chem_ptl|"&amp;'Metrics'!$C$24</f>
+        <f>"spring_chem_ntl|"&amp;'Metrics'!$C$24</f>
         <v/>
       </c>
       <c r="E24" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_chem_ntl|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F24" s="73">
@@ -5091,9 +5107,9 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>Specific conductivity</t>
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>Total phosphorus</t>
         </is>
       </c>
       <c r="B25" s="73">
@@ -5105,11 +5121,11 @@
         <v/>
       </c>
       <c r="D25" s="73">
-        <f>"spring_chem_cond|"&amp;'Metrics'!$C$25</f>
+        <f>"spring_chem_ptl|"&amp;'Metrics'!$C$25</f>
         <v/>
       </c>
       <c r="E25" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_chem_cond|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F25" s="73">
@@ -5182,9 +5198,9 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t>pH</t>
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>Specific conductivity</t>
         </is>
       </c>
       <c r="B26" s="73">
@@ -5196,11 +5212,11 @@
         <v/>
       </c>
       <c r="D26" s="73">
-        <f>"spring_chem_ph|"&amp;'Metrics'!$C$26</f>
+        <f>"spring_chem_cond|"&amp;'Metrics'!$C$26</f>
         <v/>
       </c>
       <c r="E26" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_chem_cond|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F26" s="73">
@@ -5273,9 +5289,9 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>Turbidity</t>
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>pH</t>
         </is>
       </c>
       <c r="B27" s="73">
@@ -5287,11 +5303,11 @@
         <v/>
       </c>
       <c r="D27" s="73">
-        <f>"spring_chem_turb|"&amp;'Metrics'!$C$27</f>
+        <f>"spring_chem_ph|"&amp;'Metrics'!$C$27</f>
         <v/>
       </c>
       <c r="E27" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F27" s="73">
@@ -5364,9 +5380,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>Fast-water / riffle habitat</t>
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>Turbidity</t>
         </is>
       </c>
       <c r="B28" s="73">
@@ -5378,11 +5394,11 @@
         <v/>
       </c>
       <c r="D28" s="73">
-        <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$28</f>
+        <f>"spring_chem_turb|"&amp;'Metrics'!$C$28</f>
         <v/>
       </c>
       <c r="E28" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F28" s="73">
@@ -5455,9 +5471,9 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
-        <is>
-          <t>Natural fish cover</t>
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Fast-water / riffle habitat</t>
         </is>
       </c>
       <c r="B29" s="73">
@@ -5469,11 +5485,11 @@
         <v/>
       </c>
       <c r="D29" s="73">
-        <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$29</f>
+        <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$29</f>
         <v/>
       </c>
       <c r="E29" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F29" s="73">
@@ -5546,9 +5562,9 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>Native fish taxa richness</t>
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>Natural fish cover</t>
         </is>
       </c>
       <c r="B30" s="73">
@@ -5560,11 +5576,11 @@
         <v/>
       </c>
       <c r="D30" s="73">
-        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$30</f>
+        <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$30</f>
         <v/>
       </c>
       <c r="E30" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$30,curve_key,0),MATCH("spring_fish_nat_totlntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$30,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F30" s="73">
@@ -5637,9 +5653,9 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>EPT taxa richness</t>
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>Native fish taxa richness</t>
         </is>
       </c>
       <c r="B31" s="73">
@@ -5651,11 +5667,11 @@
         <v/>
       </c>
       <c r="D31" s="73">
-        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$31</f>
+        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$31</f>
         <v/>
       </c>
       <c r="E31" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$31,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$31,curve_key,0),MATCH("spring_fish_nat_totlntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F31" s="73">
@@ -5728,9 +5744,9 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>Shannon diversity (H')</t>
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>EPT taxa richness</t>
         </is>
       </c>
       <c r="B32" s="73">
@@ -5742,11 +5758,11 @@
         <v/>
       </c>
       <c r="D32" s="73">
-        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$32</f>
+        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$32</f>
         <v/>
       </c>
       <c r="E32" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$32,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$32,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F32" s="73">
@@ -5819,9 +5835,9 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>Mapped dams within one mile</t>
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>Shannon diversity (H')</t>
         </is>
       </c>
       <c r="B33" s="73">
@@ -5833,11 +5849,11 @@
         <v/>
       </c>
       <c r="D33" s="73">
-        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$33</f>
+        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$33</f>
         <v/>
       </c>
       <c r="E33" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$33,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$33,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F33" s="73">
@@ -5906,6 +5922,97 @@
       </c>
       <c r="V33" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$33),MAX(0,MIN(1,IF('Metrics'!$B$33&lt;='Metrics'!$F$33,'Metrics'!$N$33,IF('Metrics'!$B$33&gt;='Metrics'!$M$33,'Metrics'!$U$33,IF('Metrics'!$B$33&lt;='Metrics'!$G$33,IF('Metrics'!$G$33-'Metrics'!$F$33&lt;=0,'Metrics'!$O$33,'Metrics'!$N$33+('Metrics'!$B$33-'Metrics'!$F$33)/('Metrics'!$G$33-'Metrics'!$F$33)*('Metrics'!$O$33-'Metrics'!$N$33)),IF('Metrics'!$B$33&lt;='Metrics'!$H$33,IF('Metrics'!$H$33-'Metrics'!$G$33&lt;=0,'Metrics'!$P$33,'Metrics'!$O$33+('Metrics'!$B$33-'Metrics'!$G$33)/('Metrics'!$H$33-'Metrics'!$G$33)*('Metrics'!$P$33-'Metrics'!$O$33)),IF('Metrics'!$B$33&lt;='Metrics'!$I$33,IF('Metrics'!$I$33-'Metrics'!$H$33&lt;=0,'Metrics'!$Q$33,'Metrics'!$P$33+('Metrics'!$B$33-'Metrics'!$H$33)/('Metrics'!$I$33-'Metrics'!$H$33)*('Metrics'!$Q$33-'Metrics'!$P$33)),IF('Metrics'!$B$33&lt;='Metrics'!$J$33,IF('Metrics'!$J$33-'Metrics'!$I$33&lt;=0,'Metrics'!$R$33,'Metrics'!$Q$33+('Metrics'!$B$33-'Metrics'!$I$33)/('Metrics'!$J$33-'Metrics'!$I$33)*('Metrics'!$R$33-'Metrics'!$Q$33)),IF('Metrics'!$B$33&lt;='Metrics'!$K$33,IF('Metrics'!$K$33-'Metrics'!$J$33&lt;=0,'Metrics'!$S$33,'Metrics'!$R$33+('Metrics'!$B$33-'Metrics'!$J$33)/('Metrics'!$K$33-'Metrics'!$J$33)*('Metrics'!$S$33-'Metrics'!$R$33)),IF('Metrics'!$B$33&lt;='Metrics'!$L$33,IF('Metrics'!$L$33-'Metrics'!$K$33&lt;=0,'Metrics'!$T$33,'Metrics'!$S$33+('Metrics'!$B$33-'Metrics'!$K$33)/('Metrics'!$L$33-'Metrics'!$K$33)*('Metrics'!$T$33-'Metrics'!$S$33)),IF('Metrics'!$M$33-'Metrics'!$L$33&lt;=0,'Metrics'!$U$33,'Metrics'!$T$33+('Metrics'!$B$33-'Metrics'!$L$33)/('Metrics'!$M$33-'Metrics'!$L$33)*('Metrics'!$U$33-'Metrics'!$T$33)))))))))))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>Mapped dams within one mile</t>
+        </is>
+      </c>
+      <c r="B34" s="73">
+        <f>IF('DEEP Score'!$E$48="","",'DEEP Score'!$E$48)</f>
+        <v/>
+      </c>
+      <c r="C34" s="73">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D34" s="73">
+        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$34</f>
+        <v/>
+      </c>
+      <c r="E34" s="73">
+        <f>IFERROR(MATCH('Metrics'!$D$34,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F34" s="73">
+        <f>INDEX(curve_x1,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="73">
+        <f>INDEX(curve_x2,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="73">
+        <f>INDEX(curve_x3,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="73">
+        <f>INDEX(curve_x4,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="J34" s="73">
+        <f>INDEX(curve_x5,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="73">
+        <f>INDEX(curve_x6,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="73">
+        <f>INDEX(curve_x7,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="73">
+        <f>INDEX(curve_x8,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="73">
+        <f>INDEX(curve_y1,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="73">
+        <f>INDEX(curve_y2,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="73">
+        <f>INDEX(curve_y3,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="73">
+        <f>INDEX(curve_y4,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="R34" s="73">
+        <f>INDEX(curve_y5,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="S34" s="73">
+        <f>INDEX(curve_y6,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="73">
+        <f>INDEX(curve_y7,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="73">
+        <f>INDEX(curve_y8,'Metrics'!$E$34)</f>
+        <v/>
+      </c>
+      <c r="V34" s="74">
+        <f>IF(ISNUMBER('Metrics'!$B$34),MAX(0,MIN(1,IF('Metrics'!$B$34&lt;='Metrics'!$F$34,'Metrics'!$N$34,IF('Metrics'!$B$34&gt;='Metrics'!$M$34,'Metrics'!$U$34,IF('Metrics'!$B$34&lt;='Metrics'!$G$34,IF('Metrics'!$G$34-'Metrics'!$F$34&lt;=0,'Metrics'!$O$34,'Metrics'!$N$34+('Metrics'!$B$34-'Metrics'!$F$34)/('Metrics'!$G$34-'Metrics'!$F$34)*('Metrics'!$O$34-'Metrics'!$N$34)),IF('Metrics'!$B$34&lt;='Metrics'!$H$34,IF('Metrics'!$H$34-'Metrics'!$G$34&lt;=0,'Metrics'!$P$34,'Metrics'!$O$34+('Metrics'!$B$34-'Metrics'!$G$34)/('Metrics'!$H$34-'Metrics'!$G$34)*('Metrics'!$P$34-'Metrics'!$O$34)),IF('Metrics'!$B$34&lt;='Metrics'!$I$34,IF('Metrics'!$I$34-'Metrics'!$H$34&lt;=0,'Metrics'!$Q$34,'Metrics'!$P$34+('Metrics'!$B$34-'Metrics'!$H$34)/('Metrics'!$I$34-'Metrics'!$H$34)*('Metrics'!$Q$34-'Metrics'!$P$34)),IF('Metrics'!$B$34&lt;='Metrics'!$J$34,IF('Metrics'!$J$34-'Metrics'!$I$34&lt;=0,'Metrics'!$R$34,'Metrics'!$Q$34+('Metrics'!$B$34-'Metrics'!$I$34)/('Metrics'!$J$34-'Metrics'!$I$34)*('Metrics'!$R$34-'Metrics'!$Q$34)),IF('Metrics'!$B$34&lt;='Metrics'!$K$34,IF('Metrics'!$K$34-'Metrics'!$J$34&lt;=0,'Metrics'!$S$34,'Metrics'!$R$34+('Metrics'!$B$34-'Metrics'!$J$34)/('Metrics'!$K$34-'Metrics'!$J$34)*('Metrics'!$S$34-'Metrics'!$R$34)),IF('Metrics'!$B$34&lt;='Metrics'!$L$34,IF('Metrics'!$L$34-'Metrics'!$K$34&lt;=0,'Metrics'!$T$34,'Metrics'!$S$34+('Metrics'!$B$34-'Metrics'!$K$34)/('Metrics'!$L$34-'Metrics'!$K$34)*('Metrics'!$T$34-'Metrics'!$S$34)),IF('Metrics'!$M$34-'Metrics'!$L$34&lt;=0,'Metrics'!$U$34,'Metrics'!$T$34+('Metrics'!$B$34-'Metrics'!$L$34)/('Metrics'!$M$34-'Metrics'!$L$34)*('Metrics'!$U$34-'Metrics'!$T$34)))))))))))),"")</f>
         <v/>
       </c>
     </row>
@@ -5992,7 +6099,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Catchment hydrology</t>
         </is>
@@ -6001,13 +6108,13 @@
         <f>IF(COUNT('DEEP Score'!G12:G13)=0,"",SUM('DEEP Score'!G12:G13)/COUNT('DEEP Score'!G12:G13)*15)</f>
         <v/>
       </c>
-      <c r="C4" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="38" t="n">
+      <c r="C4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E4" s="38" t="n">
+      <c r="E4" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" s="73">
@@ -6036,7 +6143,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Surface water storage</t>
         </is>
@@ -6045,13 +6152,13 @@
         <f>IF(COUNT('DEEP Score'!G14:G14)=0,"",SUM('DEEP Score'!G14:G14)/COUNT('DEEP Score'!G14:G14)*15)</f>
         <v/>
       </c>
-      <c r="C5" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="38" t="n">
+      <c r="C5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F5" s="73">
@@ -6080,7 +6187,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Reach inflow</t>
         </is>
@@ -6089,13 +6196,13 @@
         <f>IF(COUNT('DEEP Score'!G15:G15)=0,"",SUM('DEEP Score'!G15:G15)/COUNT('DEEP Score'!G15:G15)*15)</f>
         <v/>
       </c>
-      <c r="C6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="38" t="n">
+      <c r="C6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F6" s="73">
@@ -6124,7 +6231,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Streamflow regime</t>
         </is>
@@ -6133,13 +6240,13 @@
         <f>IF(COUNT('DEEP Score'!G16:G17)=0,"",SUM('DEEP Score'!G16:G17)/COUNT('DEEP Score'!G16:G17)*15)</f>
         <v/>
       </c>
-      <c r="C7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="38" t="n">
+      <c r="C7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F7" s="73">
@@ -6168,7 +6275,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Low flow and baseflow dynamics</t>
         </is>
@@ -6177,13 +6284,13 @@
         <f>IF(COUNT('DEEP Score'!G18:G20)=0,"",SUM('DEEP Score'!G18:G20)/COUNT('DEEP Score'!G18:G20)*15)</f>
         <v/>
       </c>
-      <c r="C8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="38" t="n">
+      <c r="C8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F8" s="73">
@@ -6212,7 +6319,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>High flow dynamics</t>
         </is>
@@ -6221,13 +6328,13 @@
         <f>IF(COUNT('DEEP Score'!G21:G21)=0,"",SUM('DEEP Score'!G21:G21)/COUNT('DEEP Score'!G21:G21)*15)</f>
         <v/>
       </c>
-      <c r="C9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38" t="n">
+      <c r="C9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F9" s="73">
@@ -6256,7 +6363,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Floodplain connectivity</t>
         </is>
@@ -6265,13 +6372,13 @@
         <f>IF(COUNT('DEEP Score'!G22:G23)=0,"",SUM('DEEP Score'!G22:G23)/COUNT('DEEP Score'!G22:G23)*15)</f>
         <v/>
       </c>
-      <c r="C10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="38" t="n">
+      <c r="C10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E10" s="38" t="n">
+      <c r="E10" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F10" s="73">
@@ -6300,7 +6407,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Hyporheic connectivity</t>
         </is>
@@ -6309,13 +6416,13 @@
         <f>IF(COUNT('DEEP Score'!G24:G25)=0,"",SUM('DEEP Score'!G24:G25)/COUNT('DEEP Score'!G24:G25)*15)</f>
         <v/>
       </c>
-      <c r="C11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="38" t="n">
+      <c r="C11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="38" t="n">
+      <c r="E11" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F11" s="73">
@@ -6344,7 +6451,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Channel evolution</t>
         </is>
@@ -6353,13 +6460,13 @@
         <f>IF(COUNT('DEEP Score'!G26:G27)=0,"",SUM('DEEP Score'!G26:G27)/COUNT('DEEP Score'!G26:G27)*15)</f>
         <v/>
       </c>
-      <c r="C12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="38" t="n">
+      <c r="C12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="38" t="n">
+      <c r="E12" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F12" s="73">
@@ -6388,7 +6495,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Channel and floodplain dynamics</t>
         </is>
@@ -6397,13 +6504,13 @@
         <f>IF(COUNT('DEEP Score'!G28:G29)=0,"",SUM('DEEP Score'!G28:G29)/COUNT('DEEP Score'!G28:G29)*15)</f>
         <v/>
       </c>
-      <c r="C13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38" t="n">
+      <c r="C13" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" s="38" t="n">
+      <c r="E13" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F13" s="73">
@@ -6432,7 +6539,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Sediment continuity</t>
         </is>
@@ -6441,13 +6548,13 @@
         <f>IF(COUNT('DEEP Score'!G30:G31)=0,"",SUM('DEEP Score'!G30:G31)/COUNT('DEEP Score'!G30:G31)*15)</f>
         <v/>
       </c>
-      <c r="C14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="38" t="n">
+      <c r="C14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E14" s="38" t="n">
+      <c r="E14" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F14" s="73">
@@ -6476,7 +6583,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Bed composition and bedform dynamics</t>
         </is>
@@ -6485,13 +6592,13 @@
         <f>IF(COUNT('DEEP Score'!G32:G34)=0,"",SUM('DEEP Score'!G32:G34)/COUNT('DEEP Score'!G32:G34)*15)</f>
         <v/>
       </c>
-      <c r="C15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="n">
+      <c r="C15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="38" t="n">
+      <c r="E15" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F15" s="73">
@@ -6520,7 +6627,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Light &amp; thermal regime</t>
         </is>
@@ -6529,13 +6636,13 @@
         <f>IF(COUNT('DEEP Score'!G35:G36)=0,"",SUM('DEEP Score'!G35:G36)/COUNT('DEEP Score'!G35:G36)*15)</f>
         <v/>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="38" t="n">
+      <c r="D16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F16" s="73">
@@ -6564,7 +6671,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Carbon processing</t>
         </is>
@@ -6573,13 +6680,13 @@
         <f>IF(COUNT('DEEP Score'!G37:G37)=0,"",SUM('DEEP Score'!G37:G37)/COUNT('DEEP Score'!G37:G37)*15)</f>
         <v/>
       </c>
-      <c r="C17" s="38" t="n">
+      <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="38" t="n">
+      <c r="D17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F17" s="73">
@@ -6608,22 +6715,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Nutrient cycling</t>
         </is>
       </c>
       <c r="B18" s="73">
-        <f>IF(COUNT('DEEP Score'!G38:G38)=0,"",SUM('DEEP Score'!G38:G38)/COUNT('DEEP Score'!G38:G38)*15)</f>
-        <v/>
-      </c>
-      <c r="C18" s="38" t="n">
+        <f>IF(COUNT('DEEP Score'!G38:G39)=0,"",SUM('DEEP Score'!G38:G39)/COUNT('DEEP Score'!G38:G39)*15)</f>
+        <v/>
+      </c>
+      <c r="C18" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="D18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="38" t="n">
+      <c r="D18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F18" s="73">
@@ -6652,22 +6759,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Water &amp; soil quality</t>
         </is>
       </c>
       <c r="B19" s="73">
-        <f>IF(COUNT('DEEP Score'!G39:G41)=0,"",SUM('DEEP Score'!G39:G41)/COUNT('DEEP Score'!G39:G41)*15)</f>
-        <v/>
-      </c>
-      <c r="C19" s="38" t="n">
+        <f>IF(COUNT('DEEP Score'!G40:G42)=0,"",SUM('DEEP Score'!G40:G42)/COUNT('DEEP Score'!G40:G42)*15)</f>
+        <v/>
+      </c>
+      <c r="C19" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="D19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="38" t="n">
+      <c r="D19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="F19" s="73">
@@ -6696,22 +6803,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
         <is>
           <t>Habitat provision</t>
         </is>
       </c>
       <c r="B20" s="73">
-        <f>IF(COUNT('DEEP Score'!G42:G43)=0,"",SUM('DEEP Score'!G42:G43)/COUNT('DEEP Score'!G42:G43)*15)</f>
-        <v/>
-      </c>
-      <c r="C20" s="38" t="n">
+        <f>IF(COUNT('DEEP Score'!G43:G44)=0,"",SUM('DEEP Score'!G43:G44)/COUNT('DEEP Score'!G43:G44)*15)</f>
+        <v/>
+      </c>
+      <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="38" t="n">
+      <c r="D20" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="38" t="n">
+      <c r="E20" s="40" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="73">
@@ -6740,22 +6847,22 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Population support</t>
         </is>
       </c>
       <c r="B21" s="73">
-        <f>IF(COUNT('DEEP Score'!G44:G44)=0,"",SUM('DEEP Score'!G44:G44)/COUNT('DEEP Score'!G44:G44)*15)</f>
-        <v/>
-      </c>
-      <c r="C21" s="38" t="n">
+        <f>IF(COUNT('DEEP Score'!G45:G45)=0,"",SUM('DEEP Score'!G45:G45)/COUNT('DEEP Score'!G45:G45)*15)</f>
+        <v/>
+      </c>
+      <c r="C21" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="D21" s="38" t="n">
+      <c r="D21" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="38" t="n">
+      <c r="E21" s="40" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="73">
@@ -6784,22 +6891,22 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Community dynamics</t>
         </is>
       </c>
       <c r="B22" s="73">
-        <f>IF(COUNT('DEEP Score'!G45:G46)=0,"",SUM('DEEP Score'!G45:G46)/COUNT('DEEP Score'!G45:G46)*15)</f>
-        <v/>
-      </c>
-      <c r="C22" s="38" t="n">
+        <f>IF(COUNT('DEEP Score'!G46:G47)=0,"",SUM('DEEP Score'!G46:G47)/COUNT('DEEP Score'!G46:G47)*15)</f>
+        <v/>
+      </c>
+      <c r="C22" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="D22" s="38" t="n">
+      <c r="D22" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="E22" s="38" t="n">
+      <c r="E22" s="40" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="73">
@@ -6828,22 +6935,22 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Watershed connectivity</t>
         </is>
       </c>
       <c r="B23" s="73">
-        <f>IF(COUNT('DEEP Score'!G47:G47)=0,"",SUM('DEEP Score'!G47:G47)/COUNT('DEEP Score'!G47:G47)*15)</f>
-        <v/>
-      </c>
-      <c r="C23" s="38" t="n">
+        <f>IF(COUNT('DEEP Score'!G48:G48)=0,"",SUM('DEEP Score'!G48:G48)/COUNT('DEEP Score'!G48:G48)*15)</f>
+        <v/>
+      </c>
+      <c r="C23" s="40" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="38" t="n">
+      <c r="D23" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="38" t="n">
+      <c r="E23" s="40" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="73">
@@ -6884,7 +6991,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Physical</t>
         </is>
@@ -6895,7 +7002,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>Chemical</t>
         </is>
@@ -6906,7 +7013,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>Biological</t>
         </is>
@@ -6939,7 +7046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -7076,2177 +7183,2255 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>spring_pctimp2019ws|</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>spring-pctimp2019ws</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>Impervious surface</t>
+        </is>
+      </c>
+      <c r="D5" s="40" t="inlineStr"/>
+      <c r="E5" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="40" t="n">
+        <v>25.005</v>
+      </c>
+      <c r="J5" s="40" t="n">
+        <v>44.5115</v>
+      </c>
+      <c r="K5" s="40" t="n">
+        <v>44.5115</v>
+      </c>
+      <c r="L5" s="40" t="n">
+        <v>44.5115</v>
+      </c>
+      <c r="M5" s="40" t="n">
+        <v>44.5115</v>
+      </c>
+      <c r="N5" s="40" t="n">
+        <v>44.5115</v>
+      </c>
+      <c r="O5" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="40" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q5" s="40" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>spring_pctag2019ws|</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>spring-pctag2019ws</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Agriculture, crop and hay</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr"/>
-      <c r="E5" s="38" t="n">
+      <c r="D6" s="40" t="inlineStr"/>
+      <c r="E6" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="38" t="inlineStr">
-        <is>
-          <t>Fixed criteria, the same in every region</t>
-        </is>
-      </c>
-      <c r="G5" s="38" t="n">
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="38" t="n">
+      <c r="H6" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="I5" s="38" t="n">
+      <c r="I6" s="40" t="n">
         <v>50.005</v>
       </c>
-      <c r="J5" s="38" t="n">
+      <c r="J6" s="40" t="n">
         <v>76.0115</v>
       </c>
-      <c r="K5" s="38" t="n">
+      <c r="K6" s="40" t="n">
         <v>76.0115</v>
       </c>
-      <c r="L5" s="38" t="n">
+      <c r="L6" s="40" t="n">
         <v>76.0115</v>
       </c>
-      <c r="M5" s="38" t="n">
+      <c r="M6" s="40" t="n">
         <v>76.0115</v>
       </c>
-      <c r="N5" s="38" t="n">
+      <c r="N6" s="40" t="n">
         <v>76.0115</v>
       </c>
-      <c r="O5" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="38" t="n">
+      <c r="O6" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="40" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q5" s="38" t="n">
+      <c r="Q6" s="40" t="n">
         <v>0.39</v>
       </c>
-      <c r="R5" s="38" t="n">
+      <c r="R6" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="38" t="n">
+      <c r="S6" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="38" t="n">
+      <c r="T6" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="U5" s="38" t="n">
+      <c r="U6" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="38" t="n">
+      <c r="V6" s="40" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>spring_pctimp2019ws|</t>
-        </is>
-      </c>
-      <c r="B6" s="38" t="inlineStr">
-        <is>
-          <t>spring-pctimp2019ws</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="inlineStr">
-        <is>
-          <t>Impervious surface</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="inlineStr"/>
-      <c r="E6" s="38" t="n">
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>spring_pctwet2019ws|</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>spring-pctwet2019ws</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>Wetland</t>
+        </is>
+      </c>
+      <c r="D7" s="40" t="inlineStr"/>
+      <c r="E7" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N7" s="40" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>spring_rddensws|</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>spring-rddensws</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>Road density</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="inlineStr"/>
+      <c r="E8" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="38" t="inlineStr">
-        <is>
-          <t>Fixed criteria, the same in every region</t>
-        </is>
-      </c>
-      <c r="G6" s="38" t="n">
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" s="38" t="n">
-        <v>25.005</v>
-      </c>
-      <c r="J6" s="38" t="n">
-        <v>44.5115</v>
-      </c>
-      <c r="K6" s="38" t="n">
-        <v>44.5115</v>
-      </c>
-      <c r="L6" s="38" t="n">
-        <v>44.5115</v>
-      </c>
-      <c r="M6" s="38" t="n">
-        <v>44.5115</v>
-      </c>
-      <c r="N6" s="38" t="n">
-        <v>44.5115</v>
-      </c>
-      <c r="O6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="38" t="n">
+      <c r="H8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K8" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L8" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M8" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N8" s="40" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O8" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="40" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q6" s="38" t="n">
+      <c r="Q8" s="40" t="n">
         <v>0.39</v>
       </c>
-      <c r="R6" s="38" t="n">
+      <c r="R8" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="38" t="n">
+      <c r="S8" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="38" t="n">
+      <c r="T8" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="38" t="n">
+      <c r="U8" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="38" t="n">
+      <c r="V8" s="40" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>spring_pctwet2019ws|</t>
-        </is>
-      </c>
-      <c r="B7" s="38" t="inlineStr">
-        <is>
-          <t>spring-pctwet2019ws</t>
-        </is>
-      </c>
-      <c r="C7" s="38" t="inlineStr">
-        <is>
-          <t>Wetland</t>
-        </is>
-      </c>
-      <c r="D7" s="38" t="inlineStr"/>
-      <c r="E7" s="38" t="n">
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>spring_bfiws|</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>spring-bfiws</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>Base flow index</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr"/>
+      <c r="E9" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="40" t="n">
+        <v>9.428571428571429</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <v>47.9962</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>55.79506</v>
+      </c>
+      <c r="L9" s="40" t="n">
+        <v>55.79506</v>
+      </c>
+      <c r="M9" s="40" t="n">
+        <v>55.79506</v>
+      </c>
+      <c r="N9" s="40" t="n">
+        <v>55.79506</v>
+      </c>
+      <c r="O9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q9" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>spring_dorws|</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>spring-dorws</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>Degree of regulation</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr"/>
+      <c r="E10" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="38" t="inlineStr"/>
-      <c r="G7" s="38" t="n">
+      <c r="I10" s="40" t="n">
+        <v>15.005</v>
+      </c>
+      <c r="J10" s="40" t="n">
+        <v>31.9115</v>
+      </c>
+      <c r="K10" s="40" t="n">
+        <v>31.9115</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>31.9115</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>31.9115</v>
+      </c>
+      <c r="N10" s="40" t="n">
+        <v>31.9115</v>
+      </c>
+      <c r="O10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="40" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q10" s="40" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R10" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N7" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O7" s="38" t="n">
+      <c r="S10" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>spring_rddensws|</t>
-        </is>
-      </c>
-      <c r="B8" s="38" t="inlineStr">
-        <is>
-          <t>spring-rddensws</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t>Road density</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="inlineStr"/>
-      <c r="E8" s="38" t="n">
+      <c r="T10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_bfwd_rat|</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-bfwd-rat</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>Bankfull width:depth ratio</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr"/>
+      <c r="E11" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>5.479384696483613</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>10.44101786613464</v>
+      </c>
+      <c r="J11" s="40" t="n">
+        <v>24.61711263656616</v>
+      </c>
+      <c r="K11" s="40" t="n">
+        <v>29.57874580621719</v>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>38.79320740699768</v>
+      </c>
+      <c r="M11" s="40" t="n">
+        <v>52.9693021774292</v>
+      </c>
+      <c r="N11" s="40" t="n">
+        <v>52.9693021774292</v>
+      </c>
+      <c r="O11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T11" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U11" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_rp100_cm|</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-rp100-cm</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>Residual pool depth</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr"/>
+      <c r="E12" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>18 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>3.18173851285662</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>7.424056529998779</v>
+      </c>
+      <c r="J12" s="40" t="n">
+        <v>33.83988571166992</v>
+      </c>
+      <c r="K12" s="40" t="n">
+        <v>41.76463446617127</v>
+      </c>
+      <c r="L12" s="40" t="n">
+        <v>41.76463446617127</v>
+      </c>
+      <c r="M12" s="40" t="n">
+        <v>41.76463446617127</v>
+      </c>
+      <c r="N12" s="40" t="n">
+        <v>41.76463446617127</v>
+      </c>
+      <c r="O12" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q12" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_xbkf_h|</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-xbkf-h</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Bankfull height above channel</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr"/>
+      <c r="E13" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>0.01818183064460754</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>0.2176136426627636</v>
+      </c>
+      <c r="J13" s="40" t="n">
+        <v>0.3250000029802322</v>
+      </c>
+      <c r="K13" s="40" t="n">
+        <v>0.6318181753158569</v>
+      </c>
+      <c r="L13" s="40" t="n">
+        <v>0.7392045356333256</v>
+      </c>
+      <c r="M13" s="40" t="n">
+        <v>0.9386363476514816</v>
+      </c>
+      <c r="N13" s="40" t="n">
+        <v>1.245454519987106</v>
+      </c>
+      <c r="O13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q13" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R13" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U13" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V13" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_pct_safn|</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-pct-safn</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>Sand + fines</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr"/>
+      <c r="E14" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="40" t="n">
+        <v>6.493506669998169</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>36.19047546386719</v>
+      </c>
+      <c r="J14" s="40" t="n">
+        <v>75.78643385569254</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R14" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_xembed|</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-xembed</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>Embeddedness</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr"/>
+      <c r="E15" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="38" t="inlineStr">
-        <is>
-          <t>Fixed criteria, the same in every region</t>
-        </is>
-      </c>
-      <c r="G8" s="38" t="n">
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="n">
+        <v>15.79999904632568</v>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>26.47727203369141</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>62.06818199157715</v>
+      </c>
+      <c r="J15" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="O15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R15" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="38" t="n">
+      <c r="S15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_sinu|</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-sinu</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>Sinuosity</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr"/>
+      <c r="E16" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>1.030523300170898</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>1.231195569038391</v>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>1.291397249698639</v>
+      </c>
+      <c r="K16" s="40" t="n">
+        <v>1.291397249698639</v>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>1.291397249698639</v>
+      </c>
+      <c r="M16" s="40" t="n">
+        <v>1.291397249698639</v>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>1.291397249698639</v>
+      </c>
+      <c r="O16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_xbka|</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-xbka</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>Bank angle</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr"/>
+      <c r="E17" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>19.03142075538635</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>23.69318199157715</v>
+      </c>
+      <c r="J17" s="40" t="n">
+        <v>37.01249980926514</v>
+      </c>
+      <c r="K17" s="40" t="n">
+        <v>41.67426104545594</v>
+      </c>
+      <c r="L17" s="40" t="n">
+        <v>50.33181762695312</v>
+      </c>
+      <c r="M17" s="40" t="n">
+        <v>63.65113544464111</v>
+      </c>
+      <c r="N17" s="40" t="n">
+        <v>63.65113544464111</v>
+      </c>
+      <c r="O17" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P17" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T17" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U17" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_lrbs_use|</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-lrbs-use</t>
+        </is>
+      </c>
+      <c r="C18" s="40" t="inlineStr">
+        <is>
+          <t>Relative bed stability</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr"/>
+      <c r="E18" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="n">
+        <v>-3.027339339256287</v>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>-1.741486191749573</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>-0.9056816458702087</v>
+      </c>
+      <c r="J18" s="40" t="n">
+        <v>-0.4556330442428589</v>
+      </c>
+      <c r="K18" s="40" t="n">
+        <v>0.830220103263855</v>
+      </c>
+      <c r="L18" s="40" t="n">
+        <v>1.280268704891205</v>
+      </c>
+      <c r="M18" s="40" t="n">
+        <v>2.116073250770569</v>
+      </c>
+      <c r="N18" s="40" t="n">
+        <v>3.401926398277283</v>
+      </c>
+      <c r="O18" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q18" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U18" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V18" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_lsub_dmm|</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-lsub-dmm</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>Substrate size</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr"/>
+      <c r="E19" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="n">
+        <v>-1.944121440251668</v>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>-0.7447376449902852</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>0.8544407486915588</v>
+      </c>
+      <c r="J19" s="40" t="n">
+        <v>2.053824543952942</v>
+      </c>
+      <c r="K19" s="40" t="n">
+        <v>2.413639682531357</v>
+      </c>
+      <c r="L19" s="40" t="n">
+        <v>2.413639682531357</v>
+      </c>
+      <c r="M19" s="40" t="n">
+        <v>2.413639682531357</v>
+      </c>
+      <c r="N19" s="40" t="n">
+        <v>2.413639682531357</v>
+      </c>
+      <c r="O19" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q19" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_lwdeqvolm100|</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-lwdeqvolm100</t>
+        </is>
+      </c>
+      <c r="C20" s="40" t="inlineStr">
+        <is>
+          <t>Large wood volume</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr"/>
+      <c r="E20" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="40" t="n">
+        <v>0.2271428448813302</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>0.5299999713897705</v>
+      </c>
+      <c r="J20" s="40" t="n">
+        <v>2.549999952316284</v>
+      </c>
+      <c r="K20" s="40" t="n">
+        <v>3.155999946594238</v>
+      </c>
+      <c r="L20" s="40" t="n">
+        <v>3.155999946594238</v>
+      </c>
+      <c r="M20" s="40" t="n">
+        <v>3.155999946594238</v>
+      </c>
+      <c r="N20" s="40" t="n">
+        <v>3.155999946594238</v>
+      </c>
+      <c r="O20" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q20" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>spring_chem_chla|</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>spring-chem-chla</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Chlorophyll a</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr"/>
+      <c r="E21" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>24 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="n">
+        <v>0.1061549827456474</v>
+      </c>
+      <c r="H21" s="40" t="n">
+        <v>0.559349998831749</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>2.070000052452087</v>
+      </c>
+      <c r="J21" s="40" t="n">
+        <v>4.084200123945871</v>
+      </c>
+      <c r="K21" s="40" t="n">
+        <v>5.59485017756621</v>
+      </c>
+      <c r="L21" s="40" t="n">
+        <v>5.59485017756621</v>
+      </c>
+      <c r="M21" s="40" t="n">
+        <v>5.59485017756621</v>
+      </c>
+      <c r="N21" s="40" t="n">
+        <v>5.59485017756621</v>
+      </c>
+      <c r="O21" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R21" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_xcdenmid|</t>
+        </is>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-xcdenmid</t>
+        </is>
+      </c>
+      <c r="C22" s="40" t="inlineStr">
+        <is>
+          <t>Canopy density, mid-channel</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr"/>
+      <c r="E22" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>27 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="40" t="n">
+        <v>35.17952728271484</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>82.08556365966797</v>
+      </c>
+      <c r="J22" s="40" t="n">
+        <v>97.99465179443359</v>
+      </c>
+      <c r="K22" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="O22" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q22" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_xcmgw|</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-xcmgw</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Riparian veg cover, woody</t>
+        </is>
+      </c>
+      <c r="D23" s="40" t="inlineStr"/>
+      <c r="E23" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="40" t="n">
+        <v>0.3384740352630615</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>0.7897727489471436</v>
+      </c>
+      <c r="J23" s="40" t="n">
+        <v>1.610227227210999</v>
+      </c>
+      <c r="K23" s="40" t="n">
+        <v>1.856363570690155</v>
+      </c>
+      <c r="L23" s="40" t="n">
+        <v>1.856363570690155</v>
+      </c>
+      <c r="M23" s="40" t="n">
+        <v>1.856363570690155</v>
+      </c>
+      <c r="N23" s="40" t="n">
+        <v>1.856363570690155</v>
+      </c>
+      <c r="O23" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q23" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>spring_chem_ntl|</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>spring-chem-ntl</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>Total nitrogen</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="inlineStr"/>
+      <c r="E24" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="n">
+        <v>0.1203249990940094</v>
+      </c>
+      <c r="H24" s="40" t="n">
+        <v>0.1765000000596046</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>0.3637500032782555</v>
+      </c>
+      <c r="J24" s="40" t="n">
+        <v>0.6134166742364565</v>
+      </c>
+      <c r="K24" s="40" t="n">
+        <v>0.8006666774551074</v>
+      </c>
+      <c r="L24" s="40" t="n">
+        <v>0.8006666774551074</v>
+      </c>
+      <c r="M24" s="40" t="n">
+        <v>0.8006666774551074</v>
+      </c>
+      <c r="N24" s="40" t="n">
+        <v>0.8006666774551074</v>
+      </c>
+      <c r="O24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R24" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S24" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>spring_chem_ptl|</t>
+        </is>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>spring-chem-ptl</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>Total phosphorus</t>
+        </is>
+      </c>
+      <c r="D25" s="40" t="inlineStr"/>
+      <c r="E25" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="n">
+        <v>4.193524861335755</v>
+      </c>
+      <c r="H25" s="40" t="n">
+        <v>10.33924984931946</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>30.82499980926514</v>
+      </c>
+      <c r="J25" s="40" t="n">
+        <v>58.1393330891927</v>
+      </c>
+      <c r="K25" s="40" t="n">
+        <v>78.6250830491384</v>
+      </c>
+      <c r="L25" s="40" t="n">
+        <v>78.6250830491384</v>
+      </c>
+      <c r="M25" s="40" t="n">
+        <v>78.6250830491384</v>
+      </c>
+      <c r="N25" s="40" t="n">
+        <v>78.6250830491384</v>
+      </c>
+      <c r="O25" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R25" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>spring_chem_cond|</t>
+        </is>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>spring-chem-cond</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>Specific conductivity</t>
+        </is>
+      </c>
+      <c r="D26" s="40" t="inlineStr"/>
+      <c r="E26" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="n">
+        <v>19.16500043869019</v>
+      </c>
+      <c r="H26" s="40" t="n">
+        <v>35.87500095367432</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>91.57500267028809</v>
+      </c>
+      <c r="J26" s="40" t="n">
+        <v>165.8416716257731</v>
+      </c>
+      <c r="K26" s="40" t="n">
+        <v>221.5416733423869</v>
+      </c>
+      <c r="L26" s="40" t="n">
+        <v>221.5416733423869</v>
+      </c>
+      <c r="M26" s="40" t="n">
+        <v>221.5416733423869</v>
+      </c>
+      <c r="N26" s="40" t="n">
+        <v>221.5416733423869</v>
+      </c>
+      <c r="O26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R26" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S26" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>spring_chem_ph|</t>
+        </is>
+      </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>spring-chem-ph</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="inlineStr"/>
+      <c r="E27" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="n">
+        <v>6.130000591278076</v>
+      </c>
+      <c r="H27" s="40" t="n">
+        <v>6.62000036239624</v>
+      </c>
+      <c r="I27" s="40" t="n">
+        <v>6.938500213623047</v>
+      </c>
+      <c r="J27" s="40" t="n">
+        <v>7.110000133514404</v>
+      </c>
+      <c r="K27" s="40" t="n">
+        <v>7.599999904632568</v>
+      </c>
+      <c r="L27" s="40" t="n">
+        <v>7.771499824523926</v>
+      </c>
+      <c r="M27" s="40" t="n">
+        <v>8.089999675750732</v>
+      </c>
+      <c r="N27" s="40" t="n">
+        <v>8.579999446868896</v>
+      </c>
+      <c r="O27" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q27" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U27" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V27" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>spring_chem_turb|</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>spring-chem-turb</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>Turbidity</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr"/>
+      <c r="E28" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="n">
+        <v>0.5915000706911087</v>
+      </c>
+      <c r="H28" s="40" t="n">
+        <v>1.730000048875809</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>5.524999976158142</v>
+      </c>
+      <c r="J28" s="40" t="n">
+        <v>10.58499987920125</v>
+      </c>
+      <c r="K28" s="40" t="n">
+        <v>14.37999980648359</v>
+      </c>
+      <c r="L28" s="40" t="n">
+        <v>14.37999980648359</v>
+      </c>
+      <c r="M28" s="40" t="n">
+        <v>14.37999980648359</v>
+      </c>
+      <c r="N28" s="40" t="n">
+        <v>14.37999980648359</v>
+      </c>
+      <c r="O28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R28" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_pct_fast|</t>
+        </is>
+      </c>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-pct-fast</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>Fast-water / riffle habitat</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="inlineStr"/>
+      <c r="E29" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="40" t="n">
+        <v>1.642857159887041</v>
+      </c>
+      <c r="I29" s="40" t="n">
+        <v>3.833333373069763</v>
+      </c>
+      <c r="J29" s="40" t="n">
+        <v>27.75757598876953</v>
+      </c>
+      <c r="K29" s="40" t="n">
+        <v>34.93484877347946</v>
+      </c>
+      <c r="L29" s="40" t="n">
+        <v>34.93484877347946</v>
+      </c>
+      <c r="M29" s="40" t="n">
+        <v>34.93484877347946</v>
+      </c>
+      <c r="N29" s="40" t="n">
+        <v>34.93484877347946</v>
+      </c>
+      <c r="O29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q29" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>spring_phab_xfc_nat|</t>
+        </is>
+      </c>
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>spring-phab-xfc-nat</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>Natural fish cover</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr"/>
+      <c r="E30" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="40" t="n">
+        <v>0.07792208024433681</v>
+      </c>
+      <c r="I30" s="40" t="n">
+        <v>0.1818181872367859</v>
+      </c>
+      <c r="J30" s="40" t="n">
+        <v>0.6727272868156433</v>
+      </c>
+      <c r="K30" s="40" t="n">
+        <v>0.8200000166893006</v>
+      </c>
+      <c r="L30" s="40" t="n">
+        <v>0.8200000166893006</v>
+      </c>
+      <c r="M30" s="40" t="n">
+        <v>0.8200000166893006</v>
+      </c>
+      <c r="N30" s="40" t="n">
+        <v>0.8200000166893006</v>
+      </c>
+      <c r="O30" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q30" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>spring_fish_nat_totlntax|</t>
+        </is>
+      </c>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>spring-fish-nat-totlntax</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>Native fish taxa richness</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="inlineStr"/>
+      <c r="E31" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>16 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="40" t="n">
+        <v>2.464285714285714</v>
+      </c>
+      <c r="I31" s="40" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J31" s="40" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="K31" s="40" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L31" s="40" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M31" s="40" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N31" s="40" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q31" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>spring_bent_ept_ntax|</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>spring-bent-ept-ntax</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>EPT taxa richness</t>
+        </is>
+      </c>
+      <c r="D32" s="40" t="inlineStr"/>
+      <c r="E32" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="40" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="I32" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="K32" s="40" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L32" s="40" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M32" s="40" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N32" s="40" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="O32" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q32" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R32" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>spring_bent_hprime|</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>spring-bent-hprime</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>Shannon diversity (H')</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr"/>
+      <c r="E33" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="40" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="I33" s="40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J33" s="40" t="n">
+        <v>3.180000066757202</v>
+      </c>
+      <c r="K33" s="40" t="n">
+        <v>3.384000086784363</v>
+      </c>
+      <c r="L33" s="40" t="n">
+        <v>3.384000086784363</v>
+      </c>
+      <c r="M33" s="40" t="n">
+        <v>3.384000086784363</v>
+      </c>
+      <c r="N33" s="40" t="n">
+        <v>3.384000086784363</v>
+      </c>
+      <c r="O33" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q33" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>spring_nid_dams_1mi|</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>spring-nid-dams-1mi</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>Mapped dams within one mile</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="inlineStr"/>
+      <c r="E34" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K8" s="38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L8" s="38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M8" s="38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N8" s="38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O8" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="38" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Q8" s="38" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="R8" s="38" t="n">
+      <c r="K34" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="40" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="Q34" s="40" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="R34" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="38" t="n">
+      <c r="S34" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="38" t="n">
+      <c r="T34" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="38" t="n">
+      <c r="U34" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="38" t="n">
+      <c r="V34" s="40" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="38" t="inlineStr">
-        <is>
-          <t>spring_bfiws|</t>
-        </is>
-      </c>
-      <c r="B9" s="38" t="inlineStr">
-        <is>
-          <t>spring-bfiws</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>Base flow index</t>
-        </is>
-      </c>
-      <c r="D9" s="38" t="inlineStr"/>
-      <c r="E9" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="38" t="inlineStr">
-        <is>
-          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="38" t="n">
-        <v>9.428571428571429</v>
-      </c>
-      <c r="I9" s="38" t="n">
-        <v>22</v>
-      </c>
-      <c r="J9" s="38" t="n">
-        <v>47.9962</v>
-      </c>
-      <c r="K9" s="38" t="n">
-        <v>55.79506</v>
-      </c>
-      <c r="L9" s="38" t="n">
-        <v>55.79506</v>
-      </c>
-      <c r="M9" s="38" t="n">
-        <v>55.79506</v>
-      </c>
-      <c r="N9" s="38" t="n">
-        <v>55.79506</v>
-      </c>
-      <c r="O9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q9" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>spring_dorws|</t>
-        </is>
-      </c>
-      <c r="B10" s="38" t="inlineStr">
-        <is>
-          <t>spring-dorws</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Degree of regulation</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="inlineStr"/>
-      <c r="E10" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="38" t="inlineStr">
-        <is>
-          <t>Fixed criteria, the same in every region</t>
-        </is>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="38" t="n">
-        <v>15.005</v>
-      </c>
-      <c r="J10" s="38" t="n">
-        <v>31.9115</v>
-      </c>
-      <c r="K10" s="38" t="n">
-        <v>31.9115</v>
-      </c>
-      <c r="L10" s="38" t="n">
-        <v>31.9115</v>
-      </c>
-      <c r="M10" s="38" t="n">
-        <v>31.9115</v>
-      </c>
-      <c r="N10" s="38" t="n">
-        <v>31.9115</v>
-      </c>
-      <c r="O10" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="38" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Q10" s="38" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="R10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_bfwd_rat|</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-bfwd-rat</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>Bankfull width:depth ratio</t>
-        </is>
-      </c>
-      <c r="D11" s="38" t="inlineStr"/>
-      <c r="E11" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="38" t="inlineStr">
-        <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="38" t="n">
-        <v>5.479384696483613</v>
-      </c>
-      <c r="I11" s="38" t="n">
-        <v>10.44101786613464</v>
-      </c>
-      <c r="J11" s="38" t="n">
-        <v>24.61711263656616</v>
-      </c>
-      <c r="K11" s="38" t="n">
-        <v>29.57874580621719</v>
-      </c>
-      <c r="L11" s="38" t="n">
-        <v>38.79320740699768</v>
-      </c>
-      <c r="M11" s="38" t="n">
-        <v>52.9693021774292</v>
-      </c>
-      <c r="N11" s="38" t="n">
-        <v>52.9693021774292</v>
-      </c>
-      <c r="O11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T11" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_rp100_cm|</t>
-        </is>
-      </c>
-      <c r="B12" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-rp100-cm</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>Residual pool depth</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="inlineStr"/>
-      <c r="E12" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="38" t="inlineStr">
-        <is>
-          <t>18 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="38" t="n">
-        <v>3.18173851285662</v>
-      </c>
-      <c r="I12" s="38" t="n">
-        <v>7.424056529998779</v>
-      </c>
-      <c r="J12" s="38" t="n">
-        <v>33.83988571166992</v>
-      </c>
-      <c r="K12" s="38" t="n">
-        <v>41.76463446617127</v>
-      </c>
-      <c r="L12" s="38" t="n">
-        <v>41.76463446617127</v>
-      </c>
-      <c r="M12" s="38" t="n">
-        <v>41.76463446617127</v>
-      </c>
-      <c r="N12" s="38" t="n">
-        <v>41.76463446617127</v>
-      </c>
-      <c r="O12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q12" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_xbkf_h|</t>
-        </is>
-      </c>
-      <c r="B13" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-xbkf-h</t>
-        </is>
-      </c>
-      <c r="C13" s="38" t="inlineStr">
-        <is>
-          <t>Bankfull height above channel</t>
-        </is>
-      </c>
-      <c r="D13" s="38" t="inlineStr"/>
-      <c r="E13" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="38" t="inlineStr">
-        <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G13" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="38" t="n">
-        <v>0.01818183064460754</v>
-      </c>
-      <c r="I13" s="38" t="n">
-        <v>0.2176136426627636</v>
-      </c>
-      <c r="J13" s="38" t="n">
-        <v>0.3250000029802322</v>
-      </c>
-      <c r="K13" s="38" t="n">
-        <v>0.6318181753158569</v>
-      </c>
-      <c r="L13" s="38" t="n">
-        <v>0.7392045356333256</v>
-      </c>
-      <c r="M13" s="38" t="n">
-        <v>0.9386363476514816</v>
-      </c>
-      <c r="N13" s="38" t="n">
-        <v>1.245454519987106</v>
-      </c>
-      <c r="O13" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q13" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U13" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="V13" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_pct_safn|</t>
-        </is>
-      </c>
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-pct-safn</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>Sand + fines</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="inlineStr"/>
-      <c r="E14" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="38" t="inlineStr">
-        <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G14" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="38" t="n">
-        <v>6.493506669998169</v>
-      </c>
-      <c r="I14" s="38" t="n">
-        <v>36.19047546386719</v>
-      </c>
-      <c r="J14" s="38" t="n">
-        <v>75.78643385569254</v>
-      </c>
-      <c r="K14" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="L14" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="M14" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="N14" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="O14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R14" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S14" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_xembed|</t>
-        </is>
-      </c>
-      <c r="B15" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-xembed</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
-        <is>
-          <t>Embeddedness</t>
-        </is>
-      </c>
-      <c r="D15" s="38" t="inlineStr"/>
-      <c r="E15" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" s="38" t="inlineStr">
-        <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G15" s="38" t="n">
-        <v>15.79999904632568</v>
-      </c>
-      <c r="H15" s="38" t="n">
-        <v>26.47727203369141</v>
-      </c>
-      <c r="I15" s="38" t="n">
-        <v>62.06818199157715</v>
-      </c>
-      <c r="J15" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="K15" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="L15" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="M15" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="O15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R15" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_sinu|</t>
-        </is>
-      </c>
-      <c r="B16" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-sinu</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>Sinuosity</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="inlineStr"/>
-      <c r="E16" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="38" t="inlineStr">
-        <is>
-          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="38" t="n">
-        <v>1.030523300170898</v>
-      </c>
-      <c r="I16" s="38" t="n">
-        <v>1.231195569038391</v>
-      </c>
-      <c r="J16" s="38" t="n">
-        <v>1.291397249698639</v>
-      </c>
-      <c r="K16" s="38" t="n">
-        <v>1.291397249698639</v>
-      </c>
-      <c r="L16" s="38" t="n">
-        <v>1.291397249698639</v>
-      </c>
-      <c r="M16" s="38" t="n">
-        <v>1.291397249698639</v>
-      </c>
-      <c r="N16" s="38" t="n">
-        <v>1.291397249698639</v>
-      </c>
-      <c r="O16" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_xbka|</t>
-        </is>
-      </c>
-      <c r="B17" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-xbka</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="inlineStr">
-        <is>
-          <t>Bank angle</t>
-        </is>
-      </c>
-      <c r="D17" s="38" t="inlineStr"/>
-      <c r="E17" s="38" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="38" t="inlineStr">
-        <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G17" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="38" t="n">
-        <v>19.03142075538635</v>
-      </c>
-      <c r="I17" s="38" t="n">
-        <v>23.69318199157715</v>
-      </c>
-      <c r="J17" s="38" t="n">
-        <v>37.01249980926514</v>
-      </c>
-      <c r="K17" s="38" t="n">
-        <v>41.67426104545594</v>
-      </c>
-      <c r="L17" s="38" t="n">
-        <v>50.33181762695312</v>
-      </c>
-      <c r="M17" s="38" t="n">
-        <v>63.65113544464111</v>
-      </c>
-      <c r="N17" s="38" t="n">
-        <v>63.65113544464111</v>
-      </c>
-      <c r="O17" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P17" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q17" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T17" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U17" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_lrbs_use|</t>
-        </is>
-      </c>
-      <c r="B18" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-lrbs-use</t>
-        </is>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>Relative bed stability</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="inlineStr"/>
-      <c r="E18" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="38" t="inlineStr">
-        <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>-3.027339339256287</v>
-      </c>
-      <c r="H18" s="38" t="n">
-        <v>-1.741486191749573</v>
-      </c>
-      <c r="I18" s="38" t="n">
-        <v>-0.9056816458702087</v>
-      </c>
-      <c r="J18" s="38" t="n">
-        <v>-0.4556330442428589</v>
-      </c>
-      <c r="K18" s="38" t="n">
-        <v>0.830220103263855</v>
-      </c>
-      <c r="L18" s="38" t="n">
-        <v>1.280268704891205</v>
-      </c>
-      <c r="M18" s="38" t="n">
-        <v>2.116073250770569</v>
-      </c>
-      <c r="N18" s="38" t="n">
-        <v>3.401926398277283</v>
-      </c>
-      <c r="O18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q18" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U18" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="V18" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_lsub_dmm|</t>
-        </is>
-      </c>
-      <c r="B19" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-lsub-dmm</t>
-        </is>
-      </c>
-      <c r="C19" s="38" t="inlineStr">
-        <is>
-          <t>Substrate size</t>
-        </is>
-      </c>
-      <c r="D19" s="38" t="inlineStr"/>
-      <c r="E19" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F19" s="38" t="inlineStr">
-        <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G19" s="38" t="n">
-        <v>-1.944121440251668</v>
-      </c>
-      <c r="H19" s="38" t="n">
-        <v>-0.7447376449902852</v>
-      </c>
-      <c r="I19" s="38" t="n">
-        <v>0.8544407486915588</v>
-      </c>
-      <c r="J19" s="38" t="n">
-        <v>2.053824543952942</v>
-      </c>
-      <c r="K19" s="38" t="n">
-        <v>2.413639682531357</v>
-      </c>
-      <c r="L19" s="38" t="n">
-        <v>2.413639682531357</v>
-      </c>
-      <c r="M19" s="38" t="n">
-        <v>2.413639682531357</v>
-      </c>
-      <c r="N19" s="38" t="n">
-        <v>2.413639682531357</v>
-      </c>
-      <c r="O19" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q19" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_lwdeqvolm100|</t>
-        </is>
-      </c>
-      <c r="B20" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-lwdeqvolm100</t>
-        </is>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>Large wood volume</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="inlineStr"/>
-      <c r="E20" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" s="38" t="inlineStr">
-        <is>
-          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="38" t="n">
-        <v>0.2271428448813302</v>
-      </c>
-      <c r="I20" s="38" t="n">
-        <v>0.5299999713897705</v>
-      </c>
-      <c r="J20" s="38" t="n">
-        <v>2.549999952316284</v>
-      </c>
-      <c r="K20" s="38" t="n">
-        <v>3.155999946594238</v>
-      </c>
-      <c r="L20" s="38" t="n">
-        <v>3.155999946594238</v>
-      </c>
-      <c r="M20" s="38" t="n">
-        <v>3.155999946594238</v>
-      </c>
-      <c r="N20" s="38" t="n">
-        <v>3.155999946594238</v>
-      </c>
-      <c r="O20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q20" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t>spring_chem_chla|</t>
-        </is>
-      </c>
-      <c r="B21" s="38" t="inlineStr">
-        <is>
-          <t>spring-chem-chla</t>
-        </is>
-      </c>
-      <c r="C21" s="38" t="inlineStr">
-        <is>
-          <t>Chlorophyll a</t>
-        </is>
-      </c>
-      <c r="D21" s="38" t="inlineStr"/>
-      <c r="E21" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="38" t="inlineStr">
-        <is>
-          <t>24 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G21" s="38" t="n">
-        <v>0.1061549827456474</v>
-      </c>
-      <c r="H21" s="38" t="n">
-        <v>0.559349998831749</v>
-      </c>
-      <c r="I21" s="38" t="n">
-        <v>2.070000052452087</v>
-      </c>
-      <c r="J21" s="38" t="n">
-        <v>4.084200123945871</v>
-      </c>
-      <c r="K21" s="38" t="n">
-        <v>5.59485017756621</v>
-      </c>
-      <c r="L21" s="38" t="n">
-        <v>5.59485017756621</v>
-      </c>
-      <c r="M21" s="38" t="n">
-        <v>5.59485017756621</v>
-      </c>
-      <c r="N21" s="38" t="n">
-        <v>5.59485017756621</v>
-      </c>
-      <c r="O21" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R21" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S21" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_xcdenmid|</t>
-        </is>
-      </c>
-      <c r="B22" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-xcdenmid</t>
-        </is>
-      </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>Canopy density, mid-channel</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="inlineStr"/>
-      <c r="E22" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="38" t="inlineStr">
-        <is>
-          <t>27 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G22" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="38" t="n">
-        <v>35.17952728271484</v>
-      </c>
-      <c r="I22" s="38" t="n">
-        <v>82.08556365966797</v>
-      </c>
-      <c r="J22" s="38" t="n">
-        <v>97.99465179443359</v>
-      </c>
-      <c r="K22" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="M22" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="N22" s="38" t="n">
-        <v>100</v>
-      </c>
-      <c r="O22" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q22" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_xcmgw|</t>
-        </is>
-      </c>
-      <c r="B23" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-xcmgw</t>
-        </is>
-      </c>
-      <c r="C23" s="38" t="inlineStr">
-        <is>
-          <t>Riparian veg cover, woody</t>
-        </is>
-      </c>
-      <c r="D23" s="38" t="inlineStr"/>
-      <c r="E23" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" s="38" t="inlineStr">
-        <is>
-          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G23" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="38" t="n">
-        <v>0.3384740352630615</v>
-      </c>
-      <c r="I23" s="38" t="n">
-        <v>0.7897727489471436</v>
-      </c>
-      <c r="J23" s="38" t="n">
-        <v>1.610227227210999</v>
-      </c>
-      <c r="K23" s="38" t="n">
-        <v>1.856363570690155</v>
-      </c>
-      <c r="L23" s="38" t="n">
-        <v>1.856363570690155</v>
-      </c>
-      <c r="M23" s="38" t="n">
-        <v>1.856363570690155</v>
-      </c>
-      <c r="N23" s="38" t="n">
-        <v>1.856363570690155</v>
-      </c>
-      <c r="O23" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q23" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t>spring_chem_ptl|</t>
-        </is>
-      </c>
-      <c r="B24" s="38" t="inlineStr">
-        <is>
-          <t>spring-chem-ptl</t>
-        </is>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>Total phosphorus</t>
-        </is>
-      </c>
-      <c r="D24" s="38" t="inlineStr"/>
-      <c r="E24" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="38" t="inlineStr">
-        <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G24" s="38" t="n">
-        <v>4.193524861335755</v>
-      </c>
-      <c r="H24" s="38" t="n">
-        <v>10.33924984931946</v>
-      </c>
-      <c r="I24" s="38" t="n">
-        <v>30.82499980926514</v>
-      </c>
-      <c r="J24" s="38" t="n">
-        <v>58.1393330891927</v>
-      </c>
-      <c r="K24" s="38" t="n">
-        <v>78.6250830491384</v>
-      </c>
-      <c r="L24" s="38" t="n">
-        <v>78.6250830491384</v>
-      </c>
-      <c r="M24" s="38" t="n">
-        <v>78.6250830491384</v>
-      </c>
-      <c r="N24" s="38" t="n">
-        <v>78.6250830491384</v>
-      </c>
-      <c r="O24" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R24" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S24" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t>spring_chem_cond|</t>
-        </is>
-      </c>
-      <c r="B25" s="38" t="inlineStr">
-        <is>
-          <t>spring-chem-cond</t>
-        </is>
-      </c>
-      <c r="C25" s="38" t="inlineStr">
-        <is>
-          <t>Specific conductivity</t>
-        </is>
-      </c>
-      <c r="D25" s="38" t="inlineStr"/>
-      <c r="E25" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F25" s="38" t="inlineStr">
-        <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G25" s="38" t="n">
-        <v>19.16500043869019</v>
-      </c>
-      <c r="H25" s="38" t="n">
-        <v>35.87500095367432</v>
-      </c>
-      <c r="I25" s="38" t="n">
-        <v>91.57500267028809</v>
-      </c>
-      <c r="J25" s="38" t="n">
-        <v>165.8416716257731</v>
-      </c>
-      <c r="K25" s="38" t="n">
-        <v>221.5416733423869</v>
-      </c>
-      <c r="L25" s="38" t="n">
-        <v>221.5416733423869</v>
-      </c>
-      <c r="M25" s="38" t="n">
-        <v>221.5416733423869</v>
-      </c>
-      <c r="N25" s="38" t="n">
-        <v>221.5416733423869</v>
-      </c>
-      <c r="O25" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R25" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S25" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t>spring_chem_ph|</t>
-        </is>
-      </c>
-      <c r="B26" s="38" t="inlineStr">
-        <is>
-          <t>spring-chem-ph</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="D26" s="38" t="inlineStr"/>
-      <c r="E26" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="38" t="inlineStr">
-        <is>
-          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G26" s="38" t="n">
-        <v>6.130000591278076</v>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>6.62000036239624</v>
-      </c>
-      <c r="I26" s="38" t="n">
-        <v>6.938500213623047</v>
-      </c>
-      <c r="J26" s="38" t="n">
-        <v>7.110000133514404</v>
-      </c>
-      <c r="K26" s="38" t="n">
-        <v>7.599999904632568</v>
-      </c>
-      <c r="L26" s="38" t="n">
-        <v>7.771499824523926</v>
-      </c>
-      <c r="M26" s="38" t="n">
-        <v>8.089999675750732</v>
-      </c>
-      <c r="N26" s="38" t="n">
-        <v>8.579999446868896</v>
-      </c>
-      <c r="O26" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q26" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R26" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U26" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="V26" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>spring_chem_turb|</t>
-        </is>
-      </c>
-      <c r="B27" s="38" t="inlineStr">
-        <is>
-          <t>spring-chem-turb</t>
-        </is>
-      </c>
-      <c r="C27" s="38" t="inlineStr">
-        <is>
-          <t>Turbidity</t>
-        </is>
-      </c>
-      <c r="D27" s="38" t="inlineStr"/>
-      <c r="E27" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" s="38" t="inlineStr">
-        <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G27" s="38" t="n">
-        <v>0.5915000706911087</v>
-      </c>
-      <c r="H27" s="38" t="n">
-        <v>1.730000048875809</v>
-      </c>
-      <c r="I27" s="38" t="n">
-        <v>5.524999976158142</v>
-      </c>
-      <c r="J27" s="38" t="n">
-        <v>10.58499987920125</v>
-      </c>
-      <c r="K27" s="38" t="n">
-        <v>14.37999980648359</v>
-      </c>
-      <c r="L27" s="38" t="n">
-        <v>14.37999980648359</v>
-      </c>
-      <c r="M27" s="38" t="n">
-        <v>14.37999980648359</v>
-      </c>
-      <c r="N27" s="38" t="n">
-        <v>14.37999980648359</v>
-      </c>
-      <c r="O27" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R27" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S27" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_pct_fast|</t>
-        </is>
-      </c>
-      <c r="B28" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-pct-fast</t>
-        </is>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>Fast-water / riffle habitat</t>
-        </is>
-      </c>
-      <c r="D28" s="38" t="inlineStr"/>
-      <c r="E28" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="38" t="inlineStr">
-        <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G28" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="38" t="n">
-        <v>1.642857159887041</v>
-      </c>
-      <c r="I28" s="38" t="n">
-        <v>3.833333373069763</v>
-      </c>
-      <c r="J28" s="38" t="n">
-        <v>27.75757598876953</v>
-      </c>
-      <c r="K28" s="38" t="n">
-        <v>34.93484877347946</v>
-      </c>
-      <c r="L28" s="38" t="n">
-        <v>34.93484877347946</v>
-      </c>
-      <c r="M28" s="38" t="n">
-        <v>34.93484877347946</v>
-      </c>
-      <c r="N28" s="38" t="n">
-        <v>34.93484877347946</v>
-      </c>
-      <c r="O28" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q28" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R28" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38" t="inlineStr">
-        <is>
-          <t>spring_phab_xfc_nat|</t>
-        </is>
-      </c>
-      <c r="B29" s="38" t="inlineStr">
-        <is>
-          <t>spring-phab-xfc-nat</t>
-        </is>
-      </c>
-      <c r="C29" s="38" t="inlineStr">
-        <is>
-          <t>Natural fish cover</t>
-        </is>
-      </c>
-      <c r="D29" s="38" t="inlineStr"/>
-      <c r="E29" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="38" t="inlineStr">
-        <is>
-          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G29" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="38" t="n">
-        <v>0.07792208024433681</v>
-      </c>
-      <c r="I29" s="38" t="n">
-        <v>0.1818181872367859</v>
-      </c>
-      <c r="J29" s="38" t="n">
-        <v>0.6727272868156433</v>
-      </c>
-      <c r="K29" s="38" t="n">
-        <v>0.8200000166893006</v>
-      </c>
-      <c r="L29" s="38" t="n">
-        <v>0.8200000166893006</v>
-      </c>
-      <c r="M29" s="38" t="n">
-        <v>0.8200000166893006</v>
-      </c>
-      <c r="N29" s="38" t="n">
-        <v>0.8200000166893006</v>
-      </c>
-      <c r="O29" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q29" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R29" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>spring_fish_nat_totlntax|</t>
-        </is>
-      </c>
-      <c r="B30" s="38" t="inlineStr">
-        <is>
-          <t>spring-fish-nat-totlntax</t>
-        </is>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>Native fish taxa richness</t>
-        </is>
-      </c>
-      <c r="D30" s="38" t="inlineStr"/>
-      <c r="E30" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" s="38" t="inlineStr">
-        <is>
-          <t>16 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
-        </is>
-      </c>
-      <c r="G30" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="38" t="n">
-        <v>2.464285714285714</v>
-      </c>
-      <c r="I30" s="38" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J30" s="38" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="K30" s="38" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L30" s="38" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M30" s="38" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N30" s="38" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="O30" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q30" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R30" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>spring_bent_ept_ntax|</t>
-        </is>
-      </c>
-      <c r="B31" s="38" t="inlineStr">
-        <is>
-          <t>spring-bent-ept-ntax</t>
-        </is>
-      </c>
-      <c r="C31" s="38" t="inlineStr">
-        <is>
-          <t>EPT taxa richness</t>
-        </is>
-      </c>
-      <c r="D31" s="38" t="inlineStr"/>
-      <c r="E31" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="38" t="inlineStr">
-        <is>
-          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G31" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="38" t="n">
-        <v>3.857142857142857</v>
-      </c>
-      <c r="I31" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="J31" s="38" t="n">
-        <v>18</v>
-      </c>
-      <c r="K31" s="38" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="L31" s="38" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="M31" s="38" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N31" s="38" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="O31" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q31" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R31" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>spring_bent_hprime|</t>
-        </is>
-      </c>
-      <c r="B32" s="38" t="inlineStr">
-        <is>
-          <t>spring-bent-hprime</t>
-        </is>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>Shannon diversity (H')</t>
-        </is>
-      </c>
-      <c r="D32" s="38" t="inlineStr"/>
-      <c r="E32" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" s="38" t="inlineStr">
-        <is>
-          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
-        </is>
-      </c>
-      <c r="G32" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="38" t="n">
-        <v>1.071428571428571</v>
-      </c>
-      <c r="I32" s="38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J32" s="38" t="n">
-        <v>3.180000066757202</v>
-      </c>
-      <c r="K32" s="38" t="n">
-        <v>3.384000086784363</v>
-      </c>
-      <c r="L32" s="38" t="n">
-        <v>3.384000086784363</v>
-      </c>
-      <c r="M32" s="38" t="n">
-        <v>3.384000086784363</v>
-      </c>
-      <c r="N32" s="38" t="n">
-        <v>3.384000086784363</v>
-      </c>
-      <c r="O32" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="38" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q32" s="38" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R32" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" s="38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>spring_nid_dams_1mi|</t>
-        </is>
-      </c>
-      <c r="B33" s="38" t="inlineStr">
-        <is>
-          <t>spring-nid-dams-1mi</t>
-        </is>
-      </c>
-      <c r="C33" s="38" t="inlineStr">
-        <is>
-          <t>Mapped dams within one mile</t>
-        </is>
-      </c>
-      <c r="D33" s="38" t="inlineStr"/>
-      <c r="E33" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="38" t="inlineStr">
-        <is>
-          <t>Fixed criteria, the same in every region</t>
-        </is>
-      </c>
-      <c r="G33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M33" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" s="38" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" s="38" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="Q33" s="38" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="R33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="62" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="62" t="inlineStr">
         <is>
           <t>Curve sets by metric</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="62" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>Condition classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
+          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
+        <is>
+          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Outcome weights: a direct contribution counts 1, an indirect one 0.1.</t>
         </is>
@@ -9291,182 +9476,182 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Assessment id</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>interior-plateau</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Assessment name</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Interior Plateau reference assessment</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
-        <v>4</v>
+      <c r="B6" s="40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Lifecycle status</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr"/>
+      <c r="B7" s="40" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Content digest</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
-        <is>
-          <t>sha256:f987077df681b36aa080901d24ae79f2b3c61d14ce488fefdfc13daa8091074b</t>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>sha256:d339376ab846e645ef6ae9c7c41e9ea0c58f19cca552e72c7e686bf680a19f19</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>ecoregion 71 Interior Plateau</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
-        <is>
-          <t>StreamCurves reference-curve development</t>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>USEPA NRSA 2013-24 (L3 ecoregion 71), StreamCurves regional analysis, methodology 0.13-provisional</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Reference method</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>pressure-screen</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Reference screen</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>least-disturbed-v1 (strict), wadeable non-canal frame</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Scoring method</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>iqr-seed-v2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Functions scored</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n">
+      <c r="B14" s="40" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Metrics</t>
         </is>
       </c>
-      <c r="B15" s="38" t="n">
-        <v>29</v>
+      <c r="B15" s="40" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Function coverage</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>This assessment covers 20 of 20 STAF functions.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>streamcurves.deep_calculator</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>Generator version</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Formula vocabulary</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>IF AND MIN MAX INDEX MATCH IFERROR ISNUMBER COUNT SUM NA</t>
         </is>

--- a/apps/deep/www/calculators/interior-plateau.xlsx
+++ b/apps/deep/www/calculators/interior-plateau.xlsx
@@ -16,23 +16,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="curve_key">'Reference'!$A$5:$A$34</definedName>
-    <definedName name="curve_x1">'Reference'!$G$5:$G$34</definedName>
-    <definedName name="curve_y1">'Reference'!$O$5:$O$34</definedName>
-    <definedName name="curve_x2">'Reference'!$H$5:$H$34</definedName>
-    <definedName name="curve_y2">'Reference'!$P$5:$P$34</definedName>
-    <definedName name="curve_x3">'Reference'!$I$5:$I$34</definedName>
-    <definedName name="curve_y3">'Reference'!$Q$5:$Q$34</definedName>
-    <definedName name="curve_x4">'Reference'!$J$5:$J$34</definedName>
-    <definedName name="curve_y4">'Reference'!$R$5:$R$34</definedName>
-    <definedName name="curve_x5">'Reference'!$K$5:$K$34</definedName>
-    <definedName name="curve_y5">'Reference'!$S$5:$S$34</definedName>
-    <definedName name="curve_x6">'Reference'!$L$5:$L$34</definedName>
-    <definedName name="curve_y6">'Reference'!$T$5:$T$34</definedName>
-    <definedName name="curve_x7">'Reference'!$M$5:$M$34</definedName>
-    <definedName name="curve_y7">'Reference'!$U$5:$U$34</definedName>
-    <definedName name="curve_x8">'Reference'!$N$5:$N$34</definedName>
-    <definedName name="curve_y8">'Reference'!$V$5:$V$34</definedName>
+    <definedName name="curve_key">'Reference'!$A$5:$A$33</definedName>
+    <definedName name="curve_x1">'Reference'!$G$5:$G$33</definedName>
+    <definedName name="curve_y1">'Reference'!$O$5:$O$33</definedName>
+    <definedName name="curve_x2">'Reference'!$H$5:$H$33</definedName>
+    <definedName name="curve_y2">'Reference'!$P$5:$P$33</definedName>
+    <definedName name="curve_x3">'Reference'!$I$5:$I$33</definedName>
+    <definedName name="curve_y3">'Reference'!$Q$5:$Q$33</definedName>
+    <definedName name="curve_x4">'Reference'!$J$5:$J$33</definedName>
+    <definedName name="curve_y4">'Reference'!$R$5:$R$33</definedName>
+    <definedName name="curve_x5">'Reference'!$K$5:$K$33</definedName>
+    <definedName name="curve_y5">'Reference'!$S$5:$S$33</definedName>
+    <definedName name="curve_x6">'Reference'!$L$5:$L$33</definedName>
+    <definedName name="curve_y6">'Reference'!$T$5:$T$33</definedName>
+    <definedName name="curve_x7">'Reference'!$M$5:$M$33</definedName>
+    <definedName name="curve_y7">'Reference'!$U$5:$U$33</definedName>
+    <definedName name="curve_x8">'Reference'!$N$5:$N$33</definedName>
+    <definedName name="curve_y8">'Reference'!$V$5:$V$33</definedName>
     <definedName name="idx_spring_pctimp2019ws">'Metrics'!$V$5</definedName>
     <definedName name="idx_spring_pctag2019ws">'Metrics'!$V$6</definedName>
     <definedName name="idx_spring_pctwet2019ws">'Metrics'!$V$7</definedName>
@@ -47,22 +47,21 @@
     <definedName name="idx_spring_phab_sinu">'Metrics'!$V$16</definedName>
     <definedName name="idx_spring_phab_xbka">'Metrics'!$V$17</definedName>
     <definedName name="idx_spring_phab_lrbs_use">'Metrics'!$V$18</definedName>
-    <definedName name="idx_spring_phab_lsub_dmm">'Metrics'!$V$19</definedName>
-    <definedName name="idx_spring_phab_lwdeqvolm100">'Metrics'!$V$20</definedName>
-    <definedName name="idx_spring_chem_chla">'Metrics'!$V$21</definedName>
-    <definedName name="idx_spring_phab_xcdenmid">'Metrics'!$V$22</definedName>
-    <definedName name="idx_spring_phab_xcmgw">'Metrics'!$V$23</definedName>
-    <definedName name="idx_spring_chem_ntl">'Metrics'!$V$24</definedName>
-    <definedName name="idx_spring_chem_ptl">'Metrics'!$V$25</definedName>
-    <definedName name="idx_spring_chem_cond">'Metrics'!$V$26</definedName>
-    <definedName name="idx_spring_chem_ph">'Metrics'!$V$27</definedName>
-    <definedName name="idx_spring_chem_turb">'Metrics'!$V$28</definedName>
-    <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$29</definedName>
-    <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$30</definedName>
-    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$31</definedName>
-    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$32</definedName>
-    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$33</definedName>
-    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$34</definedName>
+    <definedName name="idx_spring_phab_lwdeqvolm100">'Metrics'!$V$19</definedName>
+    <definedName name="idx_spring_phab_lsub_dmm">'Metrics'!$V$20</definedName>
+    <definedName name="idx_spring_phab_xcdenmid">'Metrics'!$V$21</definedName>
+    <definedName name="idx_spring_phab_xcmgw">'Metrics'!$V$22</definedName>
+    <definedName name="idx_spring_chem_ntl">'Metrics'!$V$23</definedName>
+    <definedName name="idx_spring_chem_ptl">'Metrics'!$V$24</definedName>
+    <definedName name="idx_spring_chem_cond">'Metrics'!$V$25</definedName>
+    <definedName name="idx_spring_chem_ph">'Metrics'!$V$26</definedName>
+    <definedName name="idx_spring_chem_turb">'Metrics'!$V$27</definedName>
+    <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$28</definedName>
+    <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$29</definedName>
+    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$30</definedName>
+    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$31</definedName>
+    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$32</definedName>
+    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$33</definedName>
     <definedName name="fs_catchment_hydrology">'Results'!$B$4</definedName>
     <definedName name="fs_surface_water_storage">'Results'!$B$5</definedName>
     <definedName name="fs_reach_inflow">'Results'!$B$6</definedName>
@@ -106,22 +105,21 @@
     <definedName name="in_spring_phab_sinu">'DEEP Score'!$E$28</definedName>
     <definedName name="in_spring_phab_xbka">'DEEP Score'!$E$29</definedName>
     <definedName name="in_spring_phab_lrbs_use">'DEEP Score'!$E$30</definedName>
-    <definedName name="in_spring_phab_lsub_dmm">'DEEP Score'!$E$32</definedName>
-    <definedName name="in_spring_phab_lwdeqvolm100">'DEEP Score'!$E$33</definedName>
-    <definedName name="in_spring_chem_chla">'DEEP Score'!$E$35</definedName>
-    <definedName name="in_spring_phab_xcdenmid">'DEEP Score'!$E$36</definedName>
-    <definedName name="in_spring_phab_xcmgw">'DEEP Score'!$E$37</definedName>
-    <definedName name="in_spring_chem_ntl">'DEEP Score'!$E$38</definedName>
-    <definedName name="in_spring_chem_ptl">'DEEP Score'!$E$39</definedName>
-    <definedName name="in_spring_chem_cond">'DEEP Score'!$E$40</definedName>
-    <definedName name="in_spring_chem_ph">'DEEP Score'!$E$41</definedName>
-    <definedName name="in_spring_chem_turb">'DEEP Score'!$E$42</definedName>
-    <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$43</definedName>
-    <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$44</definedName>
-    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$45</definedName>
-    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$46</definedName>
-    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$47</definedName>
-    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$48</definedName>
+    <definedName name="in_spring_phab_lwdeqvolm100">'DEEP Score'!$E$32</definedName>
+    <definedName name="in_spring_phab_lsub_dmm">'DEEP Score'!$E$33</definedName>
+    <definedName name="in_spring_phab_xcdenmid">'DEEP Score'!$E$35</definedName>
+    <definedName name="in_spring_phab_xcmgw">'DEEP Score'!$E$36</definedName>
+    <definedName name="in_spring_chem_ntl">'DEEP Score'!$E$37</definedName>
+    <definedName name="in_spring_chem_ptl">'DEEP Score'!$E$38</definedName>
+    <definedName name="in_spring_chem_cond">'DEEP Score'!$E$39</definedName>
+    <definedName name="in_spring_chem_ph">'DEEP Score'!$E$40</definedName>
+    <definedName name="in_spring_chem_turb">'DEEP Score'!$E$41</definedName>
+    <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$42</definedName>
+    <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$43</definedName>
+    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$44</definedName>
+    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$45</definedName>
+    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$46</definedName>
+    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$47</definedName>
     <definedName name="site_notes">'DEEP Score'!$A$64</definedName>
     <definedName name="meta_assessment_id">'Metadata'!$B$4</definedName>
     <definedName name="meta_assessment_name">'Metadata'!$B$5</definedName>
@@ -667,10 +665,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1531,10 +1529,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 25 borrow comparable least-disturbed stations from a parent ecoregion, stating the level and the transfer risk. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
+          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 27 borrow comparable least-disturbed stations from a wider region, stating the region and the transfer risk. 22 of these curves carried forward unchanged from version 5. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1642,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Version 5 | USEPA NRSA 2013-24 (L3 ecoregion 71), StreamCurves regional analysis, methodology 0.13-provisional</t>
+          <t>Version 6 | USEPA NRSA 2013-24 (L3 ecoregion 71), StreamCurves regional analysis, methodology 0.14-provisional</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2352,12 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Substrate size</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>log mm</t>
+          <t>m3/100m</t>
         </is>
       </c>
       <c r="E32" s="14" t="n"/>
@@ -2382,12 +2380,12 @@
       <c r="B33" s="40" t="n"/>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
+          <t>Substrate size</t>
         </is>
       </c>
       <c r="D33" s="42" t="inlineStr">
         <is>
-          <t>m3/100m</t>
+          <t>log mm</t>
         </is>
       </c>
       <c r="E33" s="43" t="n"/>
@@ -2430,57 +2428,71 @@
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>Light &amp; thermal regime</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Chlorophyll a</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>ug/L</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="15" t="inlineStr"/>
-      <c r="G35" s="16">
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>Canopy density, mid-channel</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="32" t="inlineStr"/>
+      <c r="G35" s="33">
         <f>IF('Metrics'!$V$21="","",'Metrics'!$V$21)</f>
         <v/>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="34">
         <f>IF('Results'!$B$16="","",'Results'!$B$16)</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="35">
         <f>IF('DEEP Score'!$H$35="","",IF('DEEP Score'!$H$35&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$35&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n"/>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>Canopy density, mid-channel</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="24" t="inlineStr"/>
-      <c r="G36" s="25">
+      <c r="A36" s="53" t="inlineStr">
+        <is>
+          <t>Physicochemistry</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Carbon processing</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>Riparian veg cover, woody</t>
+        </is>
+      </c>
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="32" t="inlineStr"/>
+      <c r="G36" s="33">
         <f>IF('Metrics'!$V$22="","",'Metrics'!$V$22)</f>
         <v/>
       </c>
-      <c r="H36" s="20" t="n"/>
-      <c r="I36" s="26" t="n"/>
+      <c r="H36" s="34">
+        <f>IF('Results'!$B$17="","",'Results'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="I36" s="35">
+        <f>IF('DEEP Score'!$H$36="","",IF('DEEP Score'!$H$36&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$36&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="54" t="inlineStr">
@@ -2488,386 +2500,365 @@
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>Carbon processing</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>Riparian veg cover, woody</t>
-        </is>
-      </c>
-      <c r="D37" s="30" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Nutrient cycling</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Total nitrogen</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>mg N/L</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="15" t="inlineStr"/>
+      <c r="G37" s="16">
+        <f>IF('Metrics'!$V$23="","",'Metrics'!$V$23)</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
+        <v/>
+      </c>
+      <c r="I37" s="18">
+        <f>IF('DEEP Score'!$H$37="","",IF('DEEP Score'!$H$37&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$37&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Total phosphorus</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>ug/L</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="24" t="inlineStr"/>
+      <c r="G38" s="25">
+        <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
+        <v/>
+      </c>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="54" t="inlineStr">
+        <is>
+          <t>Physicochemistry</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Water &amp; soil quality</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Specific conductivity</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>uS/cm</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="15" t="inlineStr"/>
+      <c r="G39" s="16">
+        <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>IF('DEEP Score'!$H$39="","",IF('DEEP Score'!$H$39&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$39&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="n"/>
+      <c r="B40" s="40" t="n"/>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>Std. Units</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="n"/>
+      <c r="F40" s="44" t="inlineStr"/>
+      <c r="G40" s="45">
+        <f>IF('Metrics'!$V$26="","",'Metrics'!$V$26)</f>
+        <v/>
+      </c>
+      <c r="H40" s="40" t="n"/>
+      <c r="I40" s="46" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Turbidity</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>NTU</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="24" t="inlineStr"/>
+      <c r="G41" s="25">
+        <f>IF('Metrics'!$V$27="","",'Metrics'!$V$27)</f>
+        <v/>
+      </c>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Habitat provision</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Fast-water / riffle habitat</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="15" t="inlineStr"/>
+      <c r="G42" s="16">
+        <f>IF('Metrics'!$V$28="","",'Metrics'!$V$28)</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>IF('Results'!$B$20="","",'Results'!$B$20)</f>
+        <v/>
+      </c>
+      <c r="I42" s="18">
+        <f>IF('DEEP Score'!$H$42="","",IF('DEEP Score'!$H$42&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$42&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Natural fish cover</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="32" t="inlineStr"/>
-      <c r="G37" s="33">
-        <f>IF('Metrics'!$V$23="","",'Metrics'!$V$23)</f>
-        <v/>
-      </c>
-      <c r="H37" s="34">
-        <f>IF('Results'!$B$17="","",'Results'!$B$17)</f>
-        <v/>
-      </c>
-      <c r="I37" s="35">
-        <f>IF('DEEP Score'!$H$37="","",IF('DEEP Score'!$H$37&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$37&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="53" t="inlineStr">
-        <is>
-          <t>Physicochemistry</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Nutrient cycling</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>Total nitrogen</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>mg N/L</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="15" t="inlineStr"/>
-      <c r="G38" s="16">
-        <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
-        <v/>
-      </c>
-      <c r="H38" s="17">
-        <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
-        <v/>
-      </c>
-      <c r="I38" s="18">
-        <f>IF('DEEP Score'!$H$38="","",IF('DEEP Score'!$H$38&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$38&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>Total phosphorus</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="inlineStr">
-        <is>
-          <t>ug/L</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="24" t="inlineStr"/>
-      <c r="G39" s="25">
-        <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
-        <v/>
-      </c>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="26" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="53" t="inlineStr">
-        <is>
-          <t>Physicochemistry</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Water &amp; soil quality</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>Specific conductivity</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>uS/cm</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="15" t="inlineStr"/>
-      <c r="G40" s="16">
-        <f>IF('Metrics'!$V$26="","",'Metrics'!$V$26)</f>
-        <v/>
-      </c>
-      <c r="H40" s="17">
-        <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
-        <v/>
-      </c>
-      <c r="I40" s="18">
-        <f>IF('DEEP Score'!$H$40="","",IF('DEEP Score'!$H$40&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$40&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="39" t="n"/>
-      <c r="B41" s="40" t="n"/>
-      <c r="C41" s="41" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="D41" s="42" t="inlineStr">
-        <is>
-          <t>Std. Units</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="n"/>
-      <c r="F41" s="44" t="inlineStr"/>
-      <c r="G41" s="45">
-        <f>IF('Metrics'!$V$27="","",'Metrics'!$V$27)</f>
-        <v/>
-      </c>
-      <c r="H41" s="40" t="n"/>
-      <c r="I41" s="46" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="n"/>
-      <c r="B42" s="20" t="n"/>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>Turbidity</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>NTU</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="24" t="inlineStr"/>
-      <c r="G42" s="25">
-        <f>IF('Metrics'!$V$28="","",'Metrics'!$V$28)</f>
-        <v/>
-      </c>
-      <c r="H42" s="20" t="n"/>
-      <c r="I42" s="26" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="55" t="inlineStr">
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="24" t="inlineStr"/>
+      <c r="G43" s="25">
+        <f>IF('Metrics'!$V$29="","",'Metrics'!$V$29)</f>
+        <v/>
+      </c>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="26" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Habitat provision</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>Fast-water / riffle habitat</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="15" t="inlineStr"/>
-      <c r="G43" s="16">
-        <f>IF('Metrics'!$V$29="","",'Metrics'!$V$29)</f>
-        <v/>
-      </c>
-      <c r="H43" s="17">
-        <f>IF('Results'!$B$20="","",'Results'!$B$20)</f>
-        <v/>
-      </c>
-      <c r="I43" s="18">
-        <f>IF('DEEP Score'!$H$43="","",IF('DEEP Score'!$H$43&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$43&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="n"/>
-      <c r="B44" s="20" t="n"/>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>Natural fish cover</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="n"/>
-      <c r="F44" s="24" t="inlineStr"/>
-      <c r="G44" s="25">
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Population support</t>
+        </is>
+      </c>
+      <c r="C44" s="29" t="inlineStr">
+        <is>
+          <t>Native fish taxa richness</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="inlineStr"/>
+      <c r="E44" s="31" t="n"/>
+      <c r="F44" s="32" t="inlineStr"/>
+      <c r="G44" s="33">
         <f>IF('Metrics'!$V$30="","",'Metrics'!$V$30)</f>
         <v/>
       </c>
-      <c r="H44" s="20" t="n"/>
-      <c r="I44" s="26" t="n"/>
+      <c r="H44" s="34">
+        <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
+        <v/>
+      </c>
+      <c r="I44" s="35">
+        <f>IF('DEEP Score'!$H$44="","",IF('DEEP Score'!$H$44&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$44&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="56" t="inlineStr">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B45" s="28" t="inlineStr">
-        <is>
-          <t>Population support</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>Native fish taxa richness</t>
-        </is>
-      </c>
-      <c r="D45" s="30" t="inlineStr"/>
-      <c r="E45" s="31" t="n"/>
-      <c r="F45" s="32" t="inlineStr"/>
-      <c r="G45" s="33">
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Community dynamics</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>EPT taxa richness</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="15" t="inlineStr"/>
+      <c r="G45" s="16">
         <f>IF('Metrics'!$V$31="","",'Metrics'!$V$31)</f>
         <v/>
       </c>
-      <c r="H45" s="34">
-        <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
-        <v/>
-      </c>
-      <c r="I45" s="35">
+      <c r="H45" s="17">
+        <f>IF('Results'!$B$22="","",'Results'!$B$22)</f>
+        <v/>
+      </c>
+      <c r="I45" s="18">
         <f>IF('DEEP Score'!$H$45="","",IF('DEEP Score'!$H$45&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$45&lt;=10,"Functioning At-Risk","Functioning")))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Shannon diversity (H')</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>H'</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="24" t="inlineStr"/>
+      <c r="G46" s="25">
+        <f>IF('Metrics'!$V$32="","",'Metrics'!$V$32)</f>
+        <v/>
+      </c>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="26" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>Community dynamics</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>EPT taxa richness</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="15" t="inlineStr"/>
-      <c r="G46" s="16">
-        <f>IF('Metrics'!$V$32="","",'Metrics'!$V$32)</f>
-        <v/>
-      </c>
-      <c r="H46" s="17">
-        <f>IF('Results'!$B$22="","",'Results'!$B$22)</f>
-        <v/>
-      </c>
-      <c r="I46" s="18">
-        <f>IF('DEEP Score'!$H$46="","",IF('DEEP Score'!$H$46&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$46&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="19" t="n"/>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>Shannon diversity (H')</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="inlineStr">
-        <is>
-          <t>H'</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="n"/>
-      <c r="F47" s="24" t="inlineStr"/>
-      <c r="G47" s="25">
+      <c r="B47" s="28" t="inlineStr">
+        <is>
+          <t>Watershed connectivity</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>Mapped dams within one mile</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>dams</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="n"/>
+      <c r="F47" s="32" t="inlineStr"/>
+      <c r="G47" s="33">
         <f>IF('Metrics'!$V$33="","",'Metrics'!$V$33)</f>
         <v/>
       </c>
-      <c r="H47" s="20" t="n"/>
-      <c r="I47" s="26" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="56" t="inlineStr">
-        <is>
-          <t>Biology</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="inlineStr">
-        <is>
-          <t>Watershed connectivity</t>
-        </is>
-      </c>
-      <c r="C48" s="29" t="inlineStr">
-        <is>
-          <t>Mapped dams within one mile</t>
-        </is>
-      </c>
-      <c r="D48" s="30" t="inlineStr">
-        <is>
-          <t>dams</t>
-        </is>
-      </c>
-      <c r="E48" s="31" t="n"/>
-      <c r="F48" s="32" t="inlineStr"/>
-      <c r="G48" s="33">
-        <f>IF('Metrics'!$V$34="","",'Metrics'!$V$34)</f>
-        <v/>
-      </c>
-      <c r="H48" s="34">
+      <c r="H47" s="34">
         <f>IF('Results'!$B$23="","",'Results'!$B$23)</f>
         <v/>
       </c>
-      <c r="I48" s="35">
-        <f>IF('DEEP Score'!$H$48="","",IF('DEEP Score'!$H$48&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$48&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
+      <c r="I47" s="35">
+        <f>IF('DEEP Score'!$H$47="","",IF('DEEP Score'!$H$47&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$47&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="57" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="57" t="inlineStr">
-        <is>
-          <t>Summary</t>
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>Sub-index (0 to 1)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Condition</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Sub-index (0 to 1)</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
+      <c r="A51" s="58" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="B51" s="59">
+        <f>'Results'!$B$26</f>
+        <v/>
+      </c>
+      <c r="C51" s="42">
+        <f>IF('DEEP Score'!$B$51&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$51&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="58" t="inlineStr">
         <is>
-          <t>Physical</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="B52" s="59">
-        <f>'Results'!$B$26</f>
+        <f>'Results'!$B$27</f>
         <v/>
       </c>
       <c r="C52" s="42">
@@ -2878,11 +2869,11 @@
     <row r="53">
       <c r="A53" s="58" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="B53" s="59">
-        <f>'Results'!$B$27</f>
+        <f>'Results'!$B$28</f>
         <v/>
       </c>
       <c r="C53" s="42">
@@ -2890,14 +2881,14 @@
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="58" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="B54" s="59">
-        <f>'Results'!$B$28</f>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="60" t="inlineStr">
+        <is>
+          <t>Ecosystem Condition Index</t>
+        </is>
+      </c>
+      <c r="B54" s="61">
+        <f>'Results'!$B$29</f>
         <v/>
       </c>
       <c r="C54" s="42">
@@ -2905,67 +2896,64 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="60" t="inlineStr">
-        <is>
-          <t>Ecosystem Condition Index</t>
-        </is>
-      </c>
-      <c r="B55" s="61">
-        <f>'Results'!$B$29</f>
-        <v/>
-      </c>
-      <c r="C55" s="42">
-        <f>IF('DEEP Score'!$B$55&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$55&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Functions with a score: </t>
+        </is>
+      </c>
+      <c r="B55" s="4">
+        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Functions with a score: </t>
-        </is>
-      </c>
-      <c r="B56" s="4">
-        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
           <t>This assessment covers 20 of 20 STAF functions.</t>
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="62" t="inlineStr">
+        <is>
+          <t>Withheld for insufficient reference support (not scored)</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="62" t="inlineStr">
-        <is>
-          <t>Withheld for insufficient reference support (not scored)</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Tolerant individuals (%) ~ HBI</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Community dynamics</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tolerant individuals (%) ~ HBI</t>
+          <t>Benthic total taxa richness</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Community dynamics</t>
+          <t>Population support</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Benthic total taxa richness</t>
+          <t>Chlorophyll a</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Population support</t>
+          <t>Light and thermal regime</t>
         </is>
       </c>
     </row>
@@ -3044,71 +3032,67 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
-  <mergeCells count="62">
+  <mergeCells count="58">
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I45:I46"/>
     <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="H43:H44"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B46:B47"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="H32:H34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B42:B43"/>
     <mergeCell ref="I26:I27"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="I28:I29"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="I40:I42"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="I12:I13"/>
-    <mergeCell ref="H46:H47"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="I37:I38"/>
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="I24:I25"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="A64:I69"/>
+    <mergeCell ref="A39:A41"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A42:A43"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="I42:I43"/>
     <mergeCell ref="H28:H29"/>
+    <mergeCell ref="H37:H38"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="I32:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="H40:H42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B39:B41"/>
     <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="A28:A29"/>
+    <mergeCell ref="H42:H43"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B26:B27"/>
-    <mergeCell ref="I46:I47"/>
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="A30:A31"/>
   </mergeCells>
-  <conditionalFormatting sqref="G12:G48">
+  <conditionalFormatting sqref="G12:G47">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(G12),G12&lt;=0.39)</formula>
     </cfRule>
@@ -3119,7 +3103,7 @@
       <formula>AND(ISNUMBER(G12),G12&gt;0.69)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H48">
+  <conditionalFormatting sqref="H12:H47">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(ISNUMBER(H12),H12&lt;=5)</formula>
     </cfRule>
@@ -3130,7 +3114,7 @@
       <formula>AND(ISNUMBER(H12),H12&gt;10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I48">
+  <conditionalFormatting sqref="I12:I47">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>I12="Non-Functioning"</formula>
     </cfRule>
@@ -3152,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4563,7 +4547,7 @@
     <row r="19">
       <c r="A19" s="40" t="inlineStr">
         <is>
-          <t>Substrate size</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="B19" s="73">
@@ -4575,11 +4559,11 @@
         <v/>
       </c>
       <c r="D19" s="73">
-        <f>"spring_phab_lsub_dmm|"&amp;'Metrics'!$C$19</f>
+        <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$19</f>
         <v/>
       </c>
       <c r="E19" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_phab_lsub_dmm|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F19" s="73">
@@ -4654,7 +4638,7 @@
     <row r="20">
       <c r="A20" s="40" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
+          <t>Substrate size</t>
         </is>
       </c>
       <c r="B20" s="73">
@@ -4666,11 +4650,11 @@
         <v/>
       </c>
       <c r="D20" s="73">
-        <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$20</f>
+        <f>"spring_phab_lsub_dmm|"&amp;'Metrics'!$C$20</f>
         <v/>
       </c>
       <c r="E20" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_phab_lsub_dmm|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F20" s="73">
@@ -4745,7 +4729,7 @@
     <row r="21">
       <c r="A21" s="40" t="inlineStr">
         <is>
-          <t>Chlorophyll a</t>
+          <t>Canopy density, mid-channel</t>
         </is>
       </c>
       <c r="B21" s="73">
@@ -4757,11 +4741,11 @@
         <v/>
       </c>
       <c r="D21" s="73">
-        <f>"spring_chem_chla|"&amp;'Metrics'!$C$21</f>
+        <f>"spring_phab_xcdenmid|"&amp;'Metrics'!$C$21</f>
         <v/>
       </c>
       <c r="E21" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$21,curve_key,0),MATCH("spring_chem_chla|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$21,curve_key,0),MATCH("spring_phab_xcdenmid|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F21" s="73">
@@ -4836,7 +4820,7 @@
     <row r="22">
       <c r="A22" s="40" t="inlineStr">
         <is>
-          <t>Canopy density, mid-channel</t>
+          <t>Riparian veg cover, woody</t>
         </is>
       </c>
       <c r="B22" s="73">
@@ -4848,11 +4832,11 @@
         <v/>
       </c>
       <c r="D22" s="73">
-        <f>"spring_phab_xcdenmid|"&amp;'Metrics'!$C$22</f>
+        <f>"spring_phab_xcmgw|"&amp;'Metrics'!$C$22</f>
         <v/>
       </c>
       <c r="E22" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$22,curve_key,0),MATCH("spring_phab_xcdenmid|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$22,curve_key,0),MATCH("spring_phab_xcmgw|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F22" s="73">
@@ -4927,7 +4911,7 @@
     <row r="23">
       <c r="A23" s="40" t="inlineStr">
         <is>
-          <t>Riparian veg cover, woody</t>
+          <t>Total nitrogen</t>
         </is>
       </c>
       <c r="B23" s="73">
@@ -4939,11 +4923,11 @@
         <v/>
       </c>
       <c r="D23" s="73">
-        <f>"spring_phab_xcmgw|"&amp;'Metrics'!$C$23</f>
+        <f>"spring_chem_ntl|"&amp;'Metrics'!$C$23</f>
         <v/>
       </c>
       <c r="E23" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$23,curve_key,0),MATCH("spring_phab_xcmgw|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$23,curve_key,0),MATCH("spring_chem_ntl|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F23" s="73">
@@ -5018,7 +5002,7 @@
     <row r="24">
       <c r="A24" s="40" t="inlineStr">
         <is>
-          <t>Total nitrogen</t>
+          <t>Total phosphorus</t>
         </is>
       </c>
       <c r="B24" s="73">
@@ -5030,11 +5014,11 @@
         <v/>
       </c>
       <c r="D24" s="73">
-        <f>"spring_chem_ntl|"&amp;'Metrics'!$C$24</f>
+        <f>"spring_chem_ptl|"&amp;'Metrics'!$C$24</f>
         <v/>
       </c>
       <c r="E24" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_chem_ntl|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F24" s="73">
@@ -5109,7 +5093,7 @@
     <row r="25">
       <c r="A25" s="40" t="inlineStr">
         <is>
-          <t>Total phosphorus</t>
+          <t>Specific conductivity</t>
         </is>
       </c>
       <c r="B25" s="73">
@@ -5121,11 +5105,11 @@
         <v/>
       </c>
       <c r="D25" s="73">
-        <f>"spring_chem_ptl|"&amp;'Metrics'!$C$25</f>
+        <f>"spring_chem_cond|"&amp;'Metrics'!$C$25</f>
         <v/>
       </c>
       <c r="E25" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_chem_cond|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F25" s="73">
@@ -5200,7 +5184,7 @@
     <row r="26">
       <c r="A26" s="40" t="inlineStr">
         <is>
-          <t>Specific conductivity</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="B26" s="73">
@@ -5212,11 +5196,11 @@
         <v/>
       </c>
       <c r="D26" s="73">
-        <f>"spring_chem_cond|"&amp;'Metrics'!$C$26</f>
+        <f>"spring_chem_ph|"&amp;'Metrics'!$C$26</f>
         <v/>
       </c>
       <c r="E26" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_chem_cond|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F26" s="73">
@@ -5291,7 +5275,7 @@
     <row r="27">
       <c r="A27" s="40" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Turbidity</t>
         </is>
       </c>
       <c r="B27" s="73">
@@ -5303,11 +5287,11 @@
         <v/>
       </c>
       <c r="D27" s="73">
-        <f>"spring_chem_ph|"&amp;'Metrics'!$C$27</f>
+        <f>"spring_chem_turb|"&amp;'Metrics'!$C$27</f>
         <v/>
       </c>
       <c r="E27" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F27" s="73">
@@ -5382,7 +5366,7 @@
     <row r="28">
       <c r="A28" s="40" t="inlineStr">
         <is>
-          <t>Turbidity</t>
+          <t>Fast-water / riffle habitat</t>
         </is>
       </c>
       <c r="B28" s="73">
@@ -5394,11 +5378,11 @@
         <v/>
       </c>
       <c r="D28" s="73">
-        <f>"spring_chem_turb|"&amp;'Metrics'!$C$28</f>
+        <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$28</f>
         <v/>
       </c>
       <c r="E28" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F28" s="73">
@@ -5473,7 +5457,7 @@
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
-          <t>Fast-water / riffle habitat</t>
+          <t>Natural fish cover</t>
         </is>
       </c>
       <c r="B29" s="73">
@@ -5485,11 +5469,11 @@
         <v/>
       </c>
       <c r="D29" s="73">
-        <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$29</f>
+        <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$29</f>
         <v/>
       </c>
       <c r="E29" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F29" s="73">
@@ -5564,7 +5548,7 @@
     <row r="30">
       <c r="A30" s="40" t="inlineStr">
         <is>
-          <t>Natural fish cover</t>
+          <t>Native fish taxa richness</t>
         </is>
       </c>
       <c r="B30" s="73">
@@ -5576,11 +5560,11 @@
         <v/>
       </c>
       <c r="D30" s="73">
-        <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$30</f>
+        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$30</f>
         <v/>
       </c>
       <c r="E30" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$30,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$30,curve_key,0),MATCH("spring_fish_nat_totlntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F30" s="73">
@@ -5655,7 +5639,7 @@
     <row r="31">
       <c r="A31" s="40" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
+          <t>EPT taxa richness</t>
         </is>
       </c>
       <c r="B31" s="73">
@@ -5667,11 +5651,11 @@
         <v/>
       </c>
       <c r="D31" s="73">
-        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$31</f>
+        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$31</f>
         <v/>
       </c>
       <c r="E31" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$31,curve_key,0),MATCH("spring_fish_nat_totlntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$31,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F31" s="73">
@@ -5746,7 +5730,7 @@
     <row r="32">
       <c r="A32" s="40" t="inlineStr">
         <is>
-          <t>EPT taxa richness</t>
+          <t>Shannon diversity (H')</t>
         </is>
       </c>
       <c r="B32" s="73">
@@ -5758,11 +5742,11 @@
         <v/>
       </c>
       <c r="D32" s="73">
-        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$32</f>
+        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$32</f>
         <v/>
       </c>
       <c r="E32" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$32,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$32,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F32" s="73">
@@ -5837,7 +5821,7 @@
     <row r="33">
       <c r="A33" s="40" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
+          <t>Mapped dams within one mile</t>
         </is>
       </c>
       <c r="B33" s="73">
@@ -5849,11 +5833,11 @@
         <v/>
       </c>
       <c r="D33" s="73">
-        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$33</f>
+        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$33</f>
         <v/>
       </c>
       <c r="E33" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$33,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$33,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F33" s="73">
@@ -5922,97 +5906,6 @@
       </c>
       <c r="V33" s="74">
         <f>IF(ISNUMBER('Metrics'!$B$33),MAX(0,MIN(1,IF('Metrics'!$B$33&lt;='Metrics'!$F$33,'Metrics'!$N$33,IF('Metrics'!$B$33&gt;='Metrics'!$M$33,'Metrics'!$U$33,IF('Metrics'!$B$33&lt;='Metrics'!$G$33,IF('Metrics'!$G$33-'Metrics'!$F$33&lt;=0,'Metrics'!$O$33,'Metrics'!$N$33+('Metrics'!$B$33-'Metrics'!$F$33)/('Metrics'!$G$33-'Metrics'!$F$33)*('Metrics'!$O$33-'Metrics'!$N$33)),IF('Metrics'!$B$33&lt;='Metrics'!$H$33,IF('Metrics'!$H$33-'Metrics'!$G$33&lt;=0,'Metrics'!$P$33,'Metrics'!$O$33+('Metrics'!$B$33-'Metrics'!$G$33)/('Metrics'!$H$33-'Metrics'!$G$33)*('Metrics'!$P$33-'Metrics'!$O$33)),IF('Metrics'!$B$33&lt;='Metrics'!$I$33,IF('Metrics'!$I$33-'Metrics'!$H$33&lt;=0,'Metrics'!$Q$33,'Metrics'!$P$33+('Metrics'!$B$33-'Metrics'!$H$33)/('Metrics'!$I$33-'Metrics'!$H$33)*('Metrics'!$Q$33-'Metrics'!$P$33)),IF('Metrics'!$B$33&lt;='Metrics'!$J$33,IF('Metrics'!$J$33-'Metrics'!$I$33&lt;=0,'Metrics'!$R$33,'Metrics'!$Q$33+('Metrics'!$B$33-'Metrics'!$I$33)/('Metrics'!$J$33-'Metrics'!$I$33)*('Metrics'!$R$33-'Metrics'!$Q$33)),IF('Metrics'!$B$33&lt;='Metrics'!$K$33,IF('Metrics'!$K$33-'Metrics'!$J$33&lt;=0,'Metrics'!$S$33,'Metrics'!$R$33+('Metrics'!$B$33-'Metrics'!$J$33)/('Metrics'!$K$33-'Metrics'!$J$33)*('Metrics'!$S$33-'Metrics'!$R$33)),IF('Metrics'!$B$33&lt;='Metrics'!$L$33,IF('Metrics'!$L$33-'Metrics'!$K$33&lt;=0,'Metrics'!$T$33,'Metrics'!$S$33+('Metrics'!$B$33-'Metrics'!$K$33)/('Metrics'!$L$33-'Metrics'!$K$33)*('Metrics'!$T$33-'Metrics'!$S$33)),IF('Metrics'!$M$33-'Metrics'!$L$33&lt;=0,'Metrics'!$U$33,'Metrics'!$T$33+('Metrics'!$B$33-'Metrics'!$L$33)/('Metrics'!$M$33-'Metrics'!$L$33)*('Metrics'!$U$33-'Metrics'!$T$33)))))))))))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>Mapped dams within one mile</t>
-        </is>
-      </c>
-      <c r="B34" s="73">
-        <f>IF('DEEP Score'!$E$48="","",'DEEP Score'!$E$48)</f>
-        <v/>
-      </c>
-      <c r="C34" s="73">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D34" s="73">
-        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$34</f>
-        <v/>
-      </c>
-      <c r="E34" s="73">
-        <f>IFERROR(MATCH('Metrics'!$D$34,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
-        <v/>
-      </c>
-      <c r="F34" s="73">
-        <f>INDEX(curve_x1,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="73">
-        <f>INDEX(curve_x2,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="73">
-        <f>INDEX(curve_x3,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="73">
-        <f>INDEX(curve_x4,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="73">
-        <f>INDEX(curve_x5,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="73">
-        <f>INDEX(curve_x6,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="73">
-        <f>INDEX(curve_x7,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="73">
-        <f>INDEX(curve_x8,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="73">
-        <f>INDEX(curve_y1,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="O34" s="73">
-        <f>INDEX(curve_y2,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="P34" s="73">
-        <f>INDEX(curve_y3,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="73">
-        <f>INDEX(curve_y4,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="R34" s="73">
-        <f>INDEX(curve_y5,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="S34" s="73">
-        <f>INDEX(curve_y6,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="T34" s="73">
-        <f>INDEX(curve_y7,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="U34" s="73">
-        <f>INDEX(curve_y8,'Metrics'!$E$34)</f>
-        <v/>
-      </c>
-      <c r="V34" s="74">
-        <f>IF(ISNUMBER('Metrics'!$B$34),MAX(0,MIN(1,IF('Metrics'!$B$34&lt;='Metrics'!$F$34,'Metrics'!$N$34,IF('Metrics'!$B$34&gt;='Metrics'!$M$34,'Metrics'!$U$34,IF('Metrics'!$B$34&lt;='Metrics'!$G$34,IF('Metrics'!$G$34-'Metrics'!$F$34&lt;=0,'Metrics'!$O$34,'Metrics'!$N$34+('Metrics'!$B$34-'Metrics'!$F$34)/('Metrics'!$G$34-'Metrics'!$F$34)*('Metrics'!$O$34-'Metrics'!$N$34)),IF('Metrics'!$B$34&lt;='Metrics'!$H$34,IF('Metrics'!$H$34-'Metrics'!$G$34&lt;=0,'Metrics'!$P$34,'Metrics'!$O$34+('Metrics'!$B$34-'Metrics'!$G$34)/('Metrics'!$H$34-'Metrics'!$G$34)*('Metrics'!$P$34-'Metrics'!$O$34)),IF('Metrics'!$B$34&lt;='Metrics'!$I$34,IF('Metrics'!$I$34-'Metrics'!$H$34&lt;=0,'Metrics'!$Q$34,'Metrics'!$P$34+('Metrics'!$B$34-'Metrics'!$H$34)/('Metrics'!$I$34-'Metrics'!$H$34)*('Metrics'!$Q$34-'Metrics'!$P$34)),IF('Metrics'!$B$34&lt;='Metrics'!$J$34,IF('Metrics'!$J$34-'Metrics'!$I$34&lt;=0,'Metrics'!$R$34,'Metrics'!$Q$34+('Metrics'!$B$34-'Metrics'!$I$34)/('Metrics'!$J$34-'Metrics'!$I$34)*('Metrics'!$R$34-'Metrics'!$Q$34)),IF('Metrics'!$B$34&lt;='Metrics'!$K$34,IF('Metrics'!$K$34-'Metrics'!$J$34&lt;=0,'Metrics'!$S$34,'Metrics'!$R$34+('Metrics'!$B$34-'Metrics'!$J$34)/('Metrics'!$K$34-'Metrics'!$J$34)*('Metrics'!$S$34-'Metrics'!$R$34)),IF('Metrics'!$B$34&lt;='Metrics'!$L$34,IF('Metrics'!$L$34-'Metrics'!$K$34&lt;=0,'Metrics'!$T$34,'Metrics'!$S$34+('Metrics'!$B$34-'Metrics'!$K$34)/('Metrics'!$L$34-'Metrics'!$K$34)*('Metrics'!$T$34-'Metrics'!$S$34)),IF('Metrics'!$M$34-'Metrics'!$L$34&lt;=0,'Metrics'!$U$34,'Metrics'!$T$34+('Metrics'!$B$34-'Metrics'!$L$34)/('Metrics'!$M$34-'Metrics'!$L$34)*('Metrics'!$U$34-'Metrics'!$T$34)))))))))))),"")</f>
         <v/>
       </c>
     </row>
@@ -6633,7 +6526,7 @@
         </is>
       </c>
       <c r="B16" s="73">
-        <f>IF(COUNT('DEEP Score'!G35:G36)=0,"",SUM('DEEP Score'!G35:G36)/COUNT('DEEP Score'!G35:G36)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G35:G35)=0,"",SUM('DEEP Score'!G35:G35)/COUNT('DEEP Score'!G35:G35)*15)</f>
         <v/>
       </c>
       <c r="C16" s="40" t="n">
@@ -6677,7 +6570,7 @@
         </is>
       </c>
       <c r="B17" s="73">
-        <f>IF(COUNT('DEEP Score'!G37:G37)=0,"",SUM('DEEP Score'!G37:G37)/COUNT('DEEP Score'!G37:G37)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G36:G36)=0,"",SUM('DEEP Score'!G36:G36)/COUNT('DEEP Score'!G36:G36)*15)</f>
         <v/>
       </c>
       <c r="C17" s="40" t="n">
@@ -6721,7 +6614,7 @@
         </is>
       </c>
       <c r="B18" s="73">
-        <f>IF(COUNT('DEEP Score'!G38:G39)=0,"",SUM('DEEP Score'!G38:G39)/COUNT('DEEP Score'!G38:G39)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G37:G38)=0,"",SUM('DEEP Score'!G37:G38)/COUNT('DEEP Score'!G37:G38)*15)</f>
         <v/>
       </c>
       <c r="C18" s="40" t="n">
@@ -6765,7 +6658,7 @@
         </is>
       </c>
       <c r="B19" s="73">
-        <f>IF(COUNT('DEEP Score'!G40:G42)=0,"",SUM('DEEP Score'!G40:G42)/COUNT('DEEP Score'!G40:G42)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G39:G41)=0,"",SUM('DEEP Score'!G39:G41)/COUNT('DEEP Score'!G39:G41)*15)</f>
         <v/>
       </c>
       <c r="C19" s="40" t="n">
@@ -6809,7 +6702,7 @@
         </is>
       </c>
       <c r="B20" s="73">
-        <f>IF(COUNT('DEEP Score'!G43:G44)=0,"",SUM('DEEP Score'!G43:G44)/COUNT('DEEP Score'!G43:G44)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G42:G43)=0,"",SUM('DEEP Score'!G42:G43)/COUNT('DEEP Score'!G42:G43)*15)</f>
         <v/>
       </c>
       <c r="C20" s="40" t="n">
@@ -6853,7 +6746,7 @@
         </is>
       </c>
       <c r="B21" s="73">
-        <f>IF(COUNT('DEEP Score'!G45:G45)=0,"",SUM('DEEP Score'!G45:G45)/COUNT('DEEP Score'!G45:G45)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G44:G44)=0,"",SUM('DEEP Score'!G44:G44)/COUNT('DEEP Score'!G44:G44)*15)</f>
         <v/>
       </c>
       <c r="C21" s="40" t="n">
@@ -6897,7 +6790,7 @@
         </is>
       </c>
       <c r="B22" s="73">
-        <f>IF(COUNT('DEEP Score'!G46:G47)=0,"",SUM('DEEP Score'!G46:G47)/COUNT('DEEP Score'!G46:G47)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G45:G46)=0,"",SUM('DEEP Score'!G45:G46)/COUNT('DEEP Score'!G45:G46)*15)</f>
         <v/>
       </c>
       <c r="C22" s="40" t="n">
@@ -6941,7 +6834,7 @@
         </is>
       </c>
       <c r="B23" s="73">
-        <f>IF(COUNT('DEEP Score'!G48:G48)=0,"",SUM('DEEP Score'!G48:G48)/COUNT('DEEP Score'!G48:G48)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G47:G47)=0,"",SUM('DEEP Score'!G47:G47)/COUNT('DEEP Score'!G47:G47)*15)</f>
         <v/>
       </c>
       <c r="C23" s="40" t="n">
@@ -7046,7 +6939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -7204,7 +7097,7 @@
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G5" s="40" t="n">
@@ -7278,7 +7171,7 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G6" s="40" t="n">
@@ -7352,7 +7245,7 @@
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G7" s="40" t="n">
@@ -7426,7 +7319,7 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G8" s="40" t="n">
@@ -7500,7 +7393,7 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>37 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G9" s="40" t="n">
@@ -7574,7 +7467,7 @@
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G10" s="40" t="n">
@@ -7648,7 +7541,7 @@
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G11" s="40" t="n">
@@ -7722,7 +7615,7 @@
       </c>
       <c r="F12" s="40" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>18 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G12" s="40" t="n">
@@ -7796,7 +7689,7 @@
       </c>
       <c r="F13" s="40" t="inlineStr">
         <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G13" s="40" t="n">
@@ -7870,7 +7763,7 @@
       </c>
       <c r="F14" s="40" t="inlineStr">
         <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G14" s="40" t="n">
@@ -7944,7 +7837,7 @@
       </c>
       <c r="F15" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G15" s="40" t="n">
@@ -8018,7 +7911,7 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G16" s="40" t="n">
@@ -8092,7 +7985,7 @@
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G17" s="40" t="n">
@@ -8166,7 +8059,7 @@
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G18" s="40" t="n">
@@ -8221,17 +8114,17 @@
     <row r="19">
       <c r="A19" s="40" t="inlineStr">
         <is>
-          <t>spring_phab_lsub_dmm|</t>
+          <t>spring_phab_lwdeqvolm100|</t>
         </is>
       </c>
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>spring-phab-lsub-dmm</t>
+          <t>spring-phab-lwdeqvolm100</t>
         </is>
       </c>
       <c r="C19" s="40" t="inlineStr">
         <is>
-          <t>Substrate size</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="D19" s="40" t="inlineStr"/>
@@ -8240,32 +8133,32 @@
       </c>
       <c r="F19" s="40" t="inlineStr">
         <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>91 least-disturbed stations borrowed from NARS-9 region SAP under the regional screen (agriculture at most 37.8 percent), transfer risk high</t>
         </is>
       </c>
       <c r="G19" s="40" t="n">
-        <v>-1.944121440251668</v>
+        <v>0</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>-0.7447376449902852</v>
+        <v>0.07799999841621943</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>0.8544407486915588</v>
+        <v>0.181999996304512</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>2.053824543952942</v>
+        <v>4.620893001556396</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>2.413639682531357</v>
+        <v>5.952560903131962</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>2.413639682531357</v>
+        <v>5.952560903131962</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>2.413639682531357</v>
+        <v>5.952560903131962</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>2.413639682531357</v>
+        <v>5.952560903131962</v>
       </c>
       <c r="O19" s="40" t="n">
         <v>0</v>
@@ -8295,17 +8188,17 @@
     <row r="20">
       <c r="A20" s="40" t="inlineStr">
         <is>
-          <t>spring_phab_lwdeqvolm100|</t>
+          <t>spring_phab_lsub_dmm|</t>
         </is>
       </c>
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>spring-phab-lwdeqvolm100</t>
+          <t>spring-phab-lsub-dmm</t>
         </is>
       </c>
       <c r="C20" s="40" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
+          <t>Substrate size</t>
         </is>
       </c>
       <c r="D20" s="40" t="inlineStr"/>
@@ -8314,32 +8207,32 @@
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G20" s="40" t="n">
-        <v>0</v>
+        <v>-1.944121440251668</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>0.2271428448813302</v>
+        <v>-0.7447376449902852</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>0.5299999713897705</v>
+        <v>0.8544407486915588</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>2.549999952316284</v>
+        <v>2.053824543952942</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>3.155999946594238</v>
+        <v>2.413639682531357</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>3.155999946594238</v>
+        <v>2.413639682531357</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>3.155999946594238</v>
+        <v>2.413639682531357</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>3.155999946594238</v>
+        <v>2.413639682531357</v>
       </c>
       <c r="O20" s="40" t="n">
         <v>0</v>
@@ -8369,17 +8262,17 @@
     <row r="21">
       <c r="A21" s="40" t="inlineStr">
         <is>
-          <t>spring_chem_chla|</t>
+          <t>spring_phab_xcdenmid|</t>
         </is>
       </c>
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>spring-chem-chla</t>
+          <t>spring-phab-xcdenmid</t>
         </is>
       </c>
       <c r="C21" s="40" t="inlineStr">
         <is>
-          <t>Chlorophyll a</t>
+          <t>Canopy density, mid-channel</t>
         </is>
       </c>
       <c r="D21" s="40" t="inlineStr"/>
@@ -8388,72 +8281,72 @@
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>24 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>27 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G21" s="40" t="n">
-        <v>0.1061549827456474</v>
+        <v>0</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>0.559349998831749</v>
+        <v>35.17952728271484</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>2.070000052452087</v>
+        <v>82.08556365966797</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>4.084200123945871</v>
+        <v>97.99465179443359</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>5.59485017756621</v>
+        <v>100</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>5.59485017756621</v>
+        <v>100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>5.59485017756621</v>
+        <v>100</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>5.59485017756621</v>
+        <v>100</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q21" s="40" t="n">
         <v>0.7</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="40" t="inlineStr">
         <is>
-          <t>spring_phab_xcdenmid|</t>
+          <t>spring_phab_xcmgw|</t>
         </is>
       </c>
       <c r="B22" s="40" t="inlineStr">
         <is>
-          <t>spring-phab-xcdenmid</t>
+          <t>spring-phab-xcmgw</t>
         </is>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
-          <t>Canopy density, mid-channel</t>
+          <t>Riparian veg cover, woody</t>
         </is>
       </c>
       <c r="D22" s="40" t="inlineStr"/>
@@ -8462,32 +8355,32 @@
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>27 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G22" s="40" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>35.17952728271484</v>
+        <v>0.3384740352630615</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>82.08556365966797</v>
+        <v>0.7897727489471436</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>97.99465179443359</v>
+        <v>1.610227227210999</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>100</v>
+        <v>1.856363570690155</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>100</v>
+        <v>1.856363570690155</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>100</v>
+        <v>1.856363570690155</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>100</v>
+        <v>1.856363570690155</v>
       </c>
       <c r="O22" s="40" t="n">
         <v>0</v>
@@ -8517,17 +8410,17 @@
     <row r="23">
       <c r="A23" s="40" t="inlineStr">
         <is>
-          <t>spring_phab_xcmgw|</t>
+          <t>spring_chem_ntl|</t>
         </is>
       </c>
       <c r="B23" s="40" t="inlineStr">
         <is>
-          <t>spring-phab-xcmgw</t>
+          <t>spring-chem-ntl</t>
         </is>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>Riparian veg cover, woody</t>
+          <t>Total nitrogen</t>
         </is>
       </c>
       <c r="D23" s="40" t="inlineStr"/>
@@ -8536,72 +8429,72 @@
       </c>
       <c r="F23" s="40" t="inlineStr">
         <is>
-          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G23" s="40" t="n">
-        <v>0</v>
+        <v>0.1203249990940094</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>0.3384740352630615</v>
+        <v>0.1765000000596046</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>0.7897727489471436</v>
+        <v>0.3637500032782555</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>1.610227227210999</v>
+        <v>0.6134166742364565</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>1.856363570690155</v>
+        <v>0.8006666774551074</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>1.856363570690155</v>
+        <v>0.8006666774551074</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>1.856363570690155</v>
+        <v>0.8006666774551074</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>1.856363570690155</v>
+        <v>0.8006666774551074</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="40" t="n">
         <v>0.7</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="40" t="inlineStr">
         <is>
-          <t>spring_chem_ntl|</t>
+          <t>spring_chem_ptl|</t>
         </is>
       </c>
       <c r="B24" s="40" t="inlineStr">
         <is>
-          <t>spring-chem-ntl</t>
+          <t>spring-chem-ptl</t>
         </is>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>Total nitrogen</t>
+          <t>Total phosphorus</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr"/>
@@ -8610,32 +8503,32 @@
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G24" s="40" t="n">
-        <v>0.1203249990940094</v>
+        <v>4.193524861335755</v>
       </c>
       <c r="H24" s="40" t="n">
-        <v>0.1765000000596046</v>
+        <v>10.33924984931946</v>
       </c>
       <c r="I24" s="40" t="n">
-        <v>0.3637500032782555</v>
+        <v>30.82499980926514</v>
       </c>
       <c r="J24" s="40" t="n">
-        <v>0.6134166742364565</v>
+        <v>58.1393330891927</v>
       </c>
       <c r="K24" s="40" t="n">
-        <v>0.8006666774551074</v>
+        <v>78.6250830491384</v>
       </c>
       <c r="L24" s="40" t="n">
-        <v>0.8006666774551074</v>
+        <v>78.6250830491384</v>
       </c>
       <c r="M24" s="40" t="n">
-        <v>0.8006666774551074</v>
+        <v>78.6250830491384</v>
       </c>
       <c r="N24" s="40" t="n">
-        <v>0.8006666774551074</v>
+        <v>78.6250830491384</v>
       </c>
       <c r="O24" s="40" t="n">
         <v>1</v>
@@ -8665,17 +8558,17 @@
     <row r="25">
       <c r="A25" s="40" t="inlineStr">
         <is>
-          <t>spring_chem_ptl|</t>
+          <t>spring_chem_cond|</t>
         </is>
       </c>
       <c r="B25" s="40" t="inlineStr">
         <is>
-          <t>spring-chem-ptl</t>
+          <t>spring-chem-cond</t>
         </is>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>Total phosphorus</t>
+          <t>Specific conductivity</t>
         </is>
       </c>
       <c r="D25" s="40" t="inlineStr"/>
@@ -8684,32 +8577,32 @@
       </c>
       <c r="F25" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G25" s="40" t="n">
-        <v>4.193524861335755</v>
+        <v>19.16500043869019</v>
       </c>
       <c r="H25" s="40" t="n">
-        <v>10.33924984931946</v>
+        <v>35.87500095367432</v>
       </c>
       <c r="I25" s="40" t="n">
-        <v>30.82499980926514</v>
+        <v>91.57500267028809</v>
       </c>
       <c r="J25" s="40" t="n">
-        <v>58.1393330891927</v>
+        <v>165.8416716257731</v>
       </c>
       <c r="K25" s="40" t="n">
-        <v>78.6250830491384</v>
+        <v>221.5416733423869</v>
       </c>
       <c r="L25" s="40" t="n">
-        <v>78.6250830491384</v>
+        <v>221.5416733423869</v>
       </c>
       <c r="M25" s="40" t="n">
-        <v>78.6250830491384</v>
+        <v>221.5416733423869</v>
       </c>
       <c r="N25" s="40" t="n">
-        <v>78.6250830491384</v>
+        <v>221.5416733423869</v>
       </c>
       <c r="O25" s="40" t="n">
         <v>1</v>
@@ -8739,72 +8632,72 @@
     <row r="26">
       <c r="A26" s="40" t="inlineStr">
         <is>
-          <t>spring_chem_cond|</t>
+          <t>spring_chem_ph|</t>
         </is>
       </c>
       <c r="B26" s="40" t="inlineStr">
         <is>
-          <t>spring-chem-cond</t>
+          <t>spring-chem-ph</t>
         </is>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>Specific conductivity</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D26" s="40" t="inlineStr"/>
       <c r="E26" s="40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G26" s="40" t="n">
-        <v>19.16500043869019</v>
+        <v>6.130000591278076</v>
       </c>
       <c r="H26" s="40" t="n">
-        <v>35.87500095367432</v>
+        <v>6.62000036239624</v>
       </c>
       <c r="I26" s="40" t="n">
-        <v>91.57500267028809</v>
+        <v>6.938500213623047</v>
       </c>
       <c r="J26" s="40" t="n">
-        <v>165.8416716257731</v>
+        <v>7.110000133514404</v>
       </c>
       <c r="K26" s="40" t="n">
-        <v>221.5416733423869</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="L26" s="40" t="n">
-        <v>221.5416733423869</v>
+        <v>7.771499824523926</v>
       </c>
       <c r="M26" s="40" t="n">
-        <v>221.5416733423869</v>
+        <v>8.089999675750732</v>
       </c>
       <c r="N26" s="40" t="n">
-        <v>221.5416733423869</v>
+        <v>8.579999446868896</v>
       </c>
       <c r="O26" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q26" s="40" t="n">
         <v>0.7</v>
       </c>
       <c r="R26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U26" s="40" t="n">
         <v>0.3</v>
-      </c>
-      <c r="S26" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="40" t="n">
-        <v>0</v>
       </c>
       <c r="V26" s="40" t="n">
         <v>0</v>
@@ -8813,72 +8706,72 @@
     <row r="27">
       <c r="A27" s="40" t="inlineStr">
         <is>
-          <t>spring_chem_ph|</t>
+          <t>spring_chem_turb|</t>
         </is>
       </c>
       <c r="B27" s="40" t="inlineStr">
         <is>
-          <t>spring-chem-ph</t>
+          <t>spring-chem-turb</t>
         </is>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Turbidity</t>
         </is>
       </c>
       <c r="D27" s="40" t="inlineStr"/>
       <c r="E27" s="40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F27" s="40" t="inlineStr">
         <is>
-          <t>25 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G27" s="40" t="n">
-        <v>6.130000591278076</v>
+        <v>0.5915000706911087</v>
       </c>
       <c r="H27" s="40" t="n">
-        <v>6.62000036239624</v>
+        <v>1.730000048875809</v>
       </c>
       <c r="I27" s="40" t="n">
-        <v>6.938500213623047</v>
+        <v>5.524999976158142</v>
       </c>
       <c r="J27" s="40" t="n">
-        <v>7.110000133514404</v>
+        <v>10.58499987920125</v>
       </c>
       <c r="K27" s="40" t="n">
-        <v>7.599999904632568</v>
+        <v>14.37999980648359</v>
       </c>
       <c r="L27" s="40" t="n">
-        <v>7.771499824523926</v>
+        <v>14.37999980648359</v>
       </c>
       <c r="M27" s="40" t="n">
-        <v>8.089999675750732</v>
+        <v>14.37999980648359</v>
       </c>
       <c r="N27" s="40" t="n">
-        <v>8.579999446868896</v>
+        <v>14.37999980648359</v>
       </c>
       <c r="O27" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="40" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="40" t="n">
         <v>0.7</v>
       </c>
       <c r="R27" s="40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S27" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="40" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="U27" s="40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V27" s="40" t="n">
         <v>0</v>
@@ -8887,17 +8780,17 @@
     <row r="28">
       <c r="A28" s="40" t="inlineStr">
         <is>
-          <t>spring_chem_turb|</t>
+          <t>spring_phab_pct_fast|</t>
         </is>
       </c>
       <c r="B28" s="40" t="inlineStr">
         <is>
-          <t>spring-chem-turb</t>
+          <t>spring-phab-pct-fast</t>
         </is>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>Turbidity</t>
+          <t>Fast-water / riffle habitat</t>
         </is>
       </c>
       <c r="D28" s="40" t="inlineStr"/>
@@ -8906,72 +8799,72 @@
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>26 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G28" s="40" t="n">
-        <v>0.5915000706911087</v>
+        <v>0</v>
       </c>
       <c r="H28" s="40" t="n">
-        <v>1.730000048875809</v>
+        <v>1.642857159887041</v>
       </c>
       <c r="I28" s="40" t="n">
-        <v>5.524999976158142</v>
+        <v>3.833333373069763</v>
       </c>
       <c r="J28" s="40" t="n">
-        <v>10.58499987920125</v>
+        <v>27.75757598876953</v>
       </c>
       <c r="K28" s="40" t="n">
-        <v>14.37999980648359</v>
+        <v>34.93484877347946</v>
       </c>
       <c r="L28" s="40" t="n">
-        <v>14.37999980648359</v>
+        <v>34.93484877347946</v>
       </c>
       <c r="M28" s="40" t="n">
-        <v>14.37999980648359</v>
+        <v>34.93484877347946</v>
       </c>
       <c r="N28" s="40" t="n">
-        <v>14.37999980648359</v>
+        <v>34.93484877347946</v>
       </c>
       <c r="O28" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="40" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q28" s="40" t="n">
         <v>0.7</v>
       </c>
       <c r="R28" s="40" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S28" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
-          <t>spring_phab_pct_fast|</t>
+          <t>spring_phab_xfc_nat|</t>
         </is>
       </c>
       <c r="B29" s="40" t="inlineStr">
         <is>
-          <t>spring-phab-pct-fast</t>
+          <t>spring-phab-xfc-nat</t>
         </is>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>Fast-water / riffle habitat</t>
+          <t>Natural fish cover</t>
         </is>
       </c>
       <c r="D29" s="40" t="inlineStr"/>
@@ -8980,32 +8873,32 @@
       </c>
       <c r="F29" s="40" t="inlineStr">
         <is>
-          <t>27 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate, carried forward from version 5</t>
         </is>
       </c>
       <c r="G29" s="40" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="40" t="n">
-        <v>1.642857159887041</v>
+        <v>0.07792208024433681</v>
       </c>
       <c r="I29" s="40" t="n">
-        <v>3.833333373069763</v>
+        <v>0.1818181872367859</v>
       </c>
       <c r="J29" s="40" t="n">
-        <v>27.75757598876953</v>
+        <v>0.6727272868156433</v>
       </c>
       <c r="K29" s="40" t="n">
-        <v>34.93484877347946</v>
+        <v>0.8200000166893006</v>
       </c>
       <c r="L29" s="40" t="n">
-        <v>34.93484877347946</v>
+        <v>0.8200000166893006</v>
       </c>
       <c r="M29" s="40" t="n">
-        <v>34.93484877347946</v>
+        <v>0.8200000166893006</v>
       </c>
       <c r="N29" s="40" t="n">
-        <v>34.93484877347946</v>
+        <v>0.8200000166893006</v>
       </c>
       <c r="O29" s="40" t="n">
         <v>0</v>
@@ -9035,17 +8928,17 @@
     <row r="30">
       <c r="A30" s="40" t="inlineStr">
         <is>
-          <t>spring_phab_xfc_nat|</t>
+          <t>spring_fish_nat_totlntax|</t>
         </is>
       </c>
       <c r="B30" s="40" t="inlineStr">
         <is>
-          <t>spring-phab-xfc-nat</t>
+          <t>spring-fish-nat-totlntax</t>
         </is>
       </c>
       <c r="C30" s="40" t="inlineStr">
         <is>
-          <t>Natural fish cover</t>
+          <t>Native fish taxa richness</t>
         </is>
       </c>
       <c r="D30" s="40" t="inlineStr"/>
@@ -9054,32 +8947,32 @@
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>29 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains), transfer risk moderate</t>
+          <t>25 least-disturbed stations borrowed from NARS-9 region SAP under the regional screen (agriculture at most 37.8 percent), transfer risk moderate</t>
         </is>
       </c>
       <c r="G30" s="40" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="40" t="n">
-        <v>0.07792208024433681</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="I30" s="40" t="n">
-        <v>0.1818181872367859</v>
+        <v>9</v>
       </c>
       <c r="J30" s="40" t="n">
-        <v>0.6727272868156433</v>
+        <v>24</v>
       </c>
       <c r="K30" s="40" t="n">
-        <v>0.8200000166893006</v>
+        <v>28.5</v>
       </c>
       <c r="L30" s="40" t="n">
-        <v>0.8200000166893006</v>
+        <v>28.5</v>
       </c>
       <c r="M30" s="40" t="n">
-        <v>0.8200000166893006</v>
+        <v>28.5</v>
       </c>
       <c r="N30" s="40" t="n">
-        <v>0.8200000166893006</v>
+        <v>28.5</v>
       </c>
       <c r="O30" s="40" t="n">
         <v>0</v>
@@ -9109,17 +9002,17 @@
     <row r="31">
       <c r="A31" s="40" t="inlineStr">
         <is>
-          <t>spring_fish_nat_totlntax|</t>
+          <t>spring_bent_ept_ntax|</t>
         </is>
       </c>
       <c r="B31" s="40" t="inlineStr">
         <is>
-          <t>spring-fish-nat-totlntax</t>
+          <t>spring-bent-ept-ntax</t>
         </is>
       </c>
       <c r="C31" s="40" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
+          <t>EPT taxa richness</t>
         </is>
       </c>
       <c r="D31" s="40" t="inlineStr"/>
@@ -9128,32 +9021,32 @@
       </c>
       <c r="F31" s="40" t="inlineStr">
         <is>
-          <t>16 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk moderate</t>
+          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G31" s="40" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="40" t="n">
-        <v>2.464285714285714</v>
+        <v>3.857142857142857</v>
       </c>
       <c r="I31" s="40" t="n">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>14.25</v>
+        <v>18</v>
       </c>
       <c r="K31" s="40" t="n">
-        <v>16.8</v>
+        <v>20.7</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>16.8</v>
+        <v>20.7</v>
       </c>
       <c r="M31" s="40" t="n">
-        <v>16.8</v>
+        <v>20.7</v>
       </c>
       <c r="N31" s="40" t="n">
-        <v>16.8</v>
+        <v>20.7</v>
       </c>
       <c r="O31" s="40" t="n">
         <v>0</v>
@@ -9183,17 +9076,17 @@
     <row r="32">
       <c r="A32" s="40" t="inlineStr">
         <is>
-          <t>spring_bent_ept_ntax|</t>
+          <t>spring_bent_hprime|</t>
         </is>
       </c>
       <c r="B32" s="40" t="inlineStr">
         <is>
-          <t>spring-bent-ept-ntax</t>
+          <t>spring-bent-hprime</t>
         </is>
       </c>
       <c r="C32" s="40" t="inlineStr">
         <is>
-          <t>EPT taxa richness</t>
+          <t>Shannon diversity (H')</t>
         </is>
       </c>
       <c r="D32" s="40" t="inlineStr"/>
@@ -9202,32 +9095,32 @@
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high, carried forward from version 5</t>
         </is>
       </c>
       <c r="G32" s="40" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="40" t="n">
-        <v>3.857142857142857</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="I32" s="40" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="40" t="n">
-        <v>18</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="K32" s="40" t="n">
-        <v>20.7</v>
+        <v>3.384000086784363</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>20.7</v>
+        <v>3.384000086784363</v>
       </c>
       <c r="M32" s="40" t="n">
-        <v>20.7</v>
+        <v>3.384000086784363</v>
       </c>
       <c r="N32" s="40" t="n">
-        <v>20.7</v>
+        <v>3.384000086784363</v>
       </c>
       <c r="O32" s="40" t="n">
         <v>0</v>
@@ -9257,181 +9150,107 @@
     <row r="33">
       <c r="A33" s="40" t="inlineStr">
         <is>
-          <t>spring_bent_hprime|</t>
+          <t>spring_nid_dams_1mi|</t>
         </is>
       </c>
       <c r="B33" s="40" t="inlineStr">
         <is>
-          <t>spring-bent-hprime</t>
+          <t>spring-nid-dams-1mi</t>
         </is>
       </c>
       <c r="C33" s="40" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
+          <t>Mapped dams within one mile</t>
         </is>
       </c>
       <c r="D33" s="40" t="inlineStr"/>
       <c r="E33" s="40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="40" t="inlineStr">
         <is>
-          <t>17 least-disturbed stations borrowed from Level I ecoregion 8 (Eastern Temperate Forests), transfer risk high</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G33" s="40" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="40" t="n">
-        <v>1.071428571428571</v>
+        <v>1</v>
       </c>
       <c r="I33" s="40" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J33" s="40" t="n">
-        <v>3.180000066757202</v>
+        <v>3</v>
       </c>
       <c r="K33" s="40" t="n">
-        <v>3.384000086784363</v>
+        <v>3</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>3.384000086784363</v>
+        <v>3</v>
       </c>
       <c r="M33" s="40" t="n">
-        <v>3.384000086784363</v>
+        <v>3</v>
       </c>
       <c r="N33" s="40" t="n">
-        <v>3.384000086784363</v>
+        <v>3</v>
       </c>
       <c r="O33" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="40" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="Q33" s="40" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="R33" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="P33" s="40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q33" s="40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R33" s="40" t="n">
-        <v>1</v>
-      </c>
       <c r="S33" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" s="40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>spring_nid_dams_1mi|</t>
-        </is>
-      </c>
-      <c r="B34" s="40" t="inlineStr">
-        <is>
-          <t>spring-nid-dams-1mi</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>Mapped dams within one mile</t>
-        </is>
-      </c>
-      <c r="D34" s="40" t="inlineStr"/>
-      <c r="E34" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Scored against a published criterion rather than against stations from this ecoregion. The criterion carries its own definition of reference, which need not match this assessment's.</t>
-        </is>
-      </c>
-      <c r="G34" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="M34" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" s="40" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="Q34" s="40" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="R34" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="62" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t>Curve sets by metric</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="62" t="inlineStr">
+        <is>
+          <t>Condition classes</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr">
-        <is>
-          <t>Condition classes</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
+          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
-        <is>
-          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
         <is>
           <t>Outcome weights: a direct contribution counts 1, an indirect one 0.1.</t>
         </is>
@@ -9506,7 +9325,7 @@
         </is>
       </c>
       <c r="B6" s="40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -9525,7 +9344,7 @@
       </c>
       <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>sha256:d339376ab846e645ef6ae9c7c41e9ea0c58f19cca552e72c7e686bf680a19f19</t>
+          <t>sha256:c7f3ba4aab6330c47fa23613a0ca1969469bd4b99a8f5b268498601311da0f73</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9368,7 @@
       </c>
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>USEPA NRSA 2013-24 (L3 ecoregion 71), StreamCurves regional analysis, methodology 0.13-provisional</t>
+          <t>USEPA NRSA 2013-24 (L3 ecoregion 71), StreamCurves regional analysis, methodology 0.14-provisional</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9425,7 @@
         </is>
       </c>
       <c r="B15" s="40" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
